--- a/data-source/技能数据.xlsx
+++ b/data-source/技能数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0F40DA-5D01-4065-8F9C-6BE7AE2EAF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D22D29C-7558-4338-8E42-5FA0E310BBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F03E0F5E-A49D-457A-ADAE-8FAE4055FE2C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="284">
   <si>
     <t>格挡大师</t>
   </si>
@@ -1602,6 +1602,12 @@
   </si>
   <si>
     <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；Lv1-Lv10：商店购买</t>
+  </si>
+  <si>
+    <t>开放性伤口</t>
+  </si>
+  <si>
+    <t>下一次攻击会造成伤口，使目标受到的治疗效果降低35%，持续10秒</t>
   </si>
 </sst>
 </file>
@@ -3117,7 +3123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76EA8BDA-DC66-4172-AEE2-6135C3F09C61}">
-  <dimension ref="B1:U150"/>
+  <dimension ref="B1:U151"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
@@ -3767,171 +3773,193 @@
         <v>211</v>
       </c>
     </row>
-    <row r="15" spans="2:21" ht="14.65" thickBot="1">
-      <c r="B15" s="84" t="s">
+    <row r="15" spans="2:21">
+      <c r="B15" s="83" t="s">
+        <v>282</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0.38</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.41</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.44</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0.47</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0.53</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0.63</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0.66</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="O15" s="8">
+        <v>0.73</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0.77</v>
+      </c>
+      <c r="Q15" s="70">
+        <v>0.8</v>
+      </c>
+      <c r="R15" s="68"/>
+      <c r="U15" s="55"/>
+    </row>
+    <row r="16" spans="2:21" ht="14.65" thickBot="1">
+      <c r="B16" s="84" t="s">
         <v>194</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C16" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D16" s="57">
         <v>2</v>
       </c>
-      <c r="E15" s="57">
+      <c r="E16" s="57">
         <v>3</v>
       </c>
-      <c r="F15" s="57">
+      <c r="F16" s="57">
         <v>4</v>
       </c>
-      <c r="G15" s="57">
+      <c r="G16" s="57">
         <v>5</v>
       </c>
-      <c r="H15" s="57">
+      <c r="H16" s="57">
         <v>6</v>
       </c>
-      <c r="I15" s="57">
+      <c r="I16" s="57">
         <v>7</v>
       </c>
-      <c r="J15" s="57">
+      <c r="J16" s="57">
         <v>8</v>
       </c>
-      <c r="K15" s="57">
+      <c r="K16" s="57">
         <v>9</v>
       </c>
-      <c r="L15" s="18">
+      <c r="L16" s="18">
         <v>10</v>
       </c>
-      <c r="M15" s="18">
+      <c r="M16" s="18">
         <v>11</v>
       </c>
-      <c r="N15" s="18">
+      <c r="N16" s="18">
         <v>12</v>
       </c>
-      <c r="O15" s="18">
+      <c r="O16" s="18">
         <v>13</v>
       </c>
-      <c r="P15" s="18">
+      <c r="P16" s="18">
         <v>14</v>
       </c>
-      <c r="Q15" s="67">
+      <c r="Q16" s="67">
         <v>15</v>
       </c>
-      <c r="R15" s="69" t="s">
+      <c r="R16" s="69" t="s">
         <v>213</v>
       </c>
-      <c r="U15" s="55"/>
-    </row>
-    <row r="16" spans="2:21" ht="15" thickTop="1" thickBot="1">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-    </row>
-    <row r="17" spans="2:20" ht="14.65" thickTop="1">
-      <c r="B17" s="36" t="s">
+    </row>
+    <row r="17" spans="2:20" ht="15" thickTop="1" thickBot="1">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+    </row>
+    <row r="18" spans="2:20" ht="14.65" thickTop="1">
+      <c r="B18" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C18" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D18" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E18" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="38" t="s">
+      <c r="F18" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="G17" s="38" t="s">
+      <c r="G18" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="38" t="s">
+      <c r="H18" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="39" t="s">
+      <c r="I18" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="39" t="s">
+      <c r="J18" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="K17" s="39" t="s">
+      <c r="K18" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="L17" s="39" t="s">
+      <c r="L18" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="M17" s="41" t="s">
+      <c r="M18" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="N17" s="41" t="s">
+      <c r="N18" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="O17" s="41" t="s">
+      <c r="O18" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="P17" s="41" t="s">
+      <c r="P18" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="Q17" s="64" t="s">
+      <c r="Q18" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="R17" s="59" t="s">
+      <c r="R18" s="59" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="18" spans="2:20">
-      <c r="B18" s="100" t="s">
+    <row r="19" spans="2:20">
+      <c r="B19" s="100" t="s">
         <v>129</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="D18" s="12">
-        <v>2</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="68" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20">
-      <c r="B19" s="101" t="s">
-        <v>128</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="12">
         <v>2</v>
       </c>
-      <c r="E19" s="6">
-        <v>3</v>
-      </c>
+      <c r="E19" s="3"/>
       <c r="F19" s="35"/>
       <c r="G19" s="35"/>
       <c r="H19" s="35"/>
@@ -3945,12 +3973,12 @@
       <c r="P19" s="35"/>
       <c r="Q19" s="35"/>
       <c r="R19" s="68" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="2:20">
       <c r="B20" s="101" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>149</v>
@@ -3979,7 +4007,7 @@
     </row>
     <row r="21" spans="2:20">
       <c r="B21" s="101" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>149</v>
@@ -4006,9 +4034,9 @@
         <v>237</v>
       </c>
     </row>
-    <row r="22" spans="2:20" ht="27.75">
+    <row r="22" spans="2:20">
       <c r="B22" s="101" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>149</v>
@@ -4019,9 +4047,7 @@
       <c r="E22" s="6">
         <v>3</v>
       </c>
-      <c r="F22" s="6">
-        <v>4</v>
-      </c>
+      <c r="F22" s="35"/>
       <c r="G22" s="35"/>
       <c r="H22" s="35"/>
       <c r="I22" s="35"/>
@@ -4034,12 +4060,12 @@
       <c r="P22" s="35"/>
       <c r="Q22" s="35"/>
       <c r="R22" s="68" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="2:20" ht="27.75">
       <c r="B23" s="101" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>149</v>
@@ -4053,7 +4079,7 @@
       <c r="F23" s="6">
         <v>4</v>
       </c>
-      <c r="G23" s="3"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="35"/>
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
@@ -4070,7 +4096,7 @@
     </row>
     <row r="24" spans="2:20" ht="27.75">
       <c r="B24" s="101" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>149</v>
@@ -4084,9 +4110,7 @@
       <c r="F24" s="6">
         <v>4</v>
       </c>
-      <c r="G24" s="6">
-        <v>5</v>
-      </c>
+      <c r="G24" s="3"/>
       <c r="H24" s="35"/>
       <c r="I24" s="35"/>
       <c r="J24" s="35"/>
@@ -4098,12 +4122,12 @@
       <c r="P24" s="35"/>
       <c r="Q24" s="35"/>
       <c r="R24" s="68" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="2:20" ht="27.75">
       <c r="B25" s="101" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>149</v>
@@ -4136,7 +4160,7 @@
     </row>
     <row r="26" spans="2:20" ht="27.75">
       <c r="B26" s="101" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>149</v>
@@ -4169,7 +4193,7 @@
     </row>
     <row r="27" spans="2:20" ht="27.75">
       <c r="B27" s="101" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>149</v>
@@ -4186,9 +4210,7 @@
       <c r="G27" s="6">
         <v>5</v>
       </c>
-      <c r="H27" s="1">
-        <v>6</v>
-      </c>
+      <c r="H27" s="35"/>
       <c r="I27" s="35"/>
       <c r="J27" s="35"/>
       <c r="K27" s="35"/>
@@ -4199,12 +4221,12 @@
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
       <c r="R27" s="68" t="s">
-        <v>264</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="2:20" ht="27.75">
       <c r="B28" s="101" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>149</v>
@@ -4239,7 +4261,7 @@
     </row>
     <row r="29" spans="2:20" ht="27.75">
       <c r="B29" s="101" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>149</v>
@@ -4272,9 +4294,9 @@
         <v>264</v>
       </c>
     </row>
-    <row r="30" spans="2:20" ht="42" thickBot="1">
+    <row r="30" spans="2:20" ht="28.15" thickBot="1">
       <c r="B30" s="101" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>149</v>
@@ -4294,9 +4316,7 @@
       <c r="H30" s="1">
         <v>6</v>
       </c>
-      <c r="I30" s="1">
-        <v>7</v>
-      </c>
+      <c r="I30" s="35"/>
       <c r="J30" s="35"/>
       <c r="K30" s="35"/>
       <c r="L30" s="35"/>
@@ -4306,12 +4326,12 @@
       <c r="P30" s="35"/>
       <c r="Q30" s="35"/>
       <c r="R30" s="68" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" spans="2:20" ht="42" thickBot="1">
       <c r="B31" s="101" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>149</v>
@@ -4328,15 +4348,13 @@
       <c r="G31" s="6">
         <v>5</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H31" s="1">
         <v>6</v>
       </c>
-      <c r="I31" s="20">
+      <c r="I31" s="1">
         <v>7</v>
       </c>
-      <c r="J31" s="6">
-        <v>8</v>
-      </c>
+      <c r="J31" s="35"/>
       <c r="K31" s="35"/>
       <c r="L31" s="35"/>
       <c r="M31" s="35"/>
@@ -4345,15 +4363,15 @@
       <c r="P31" s="35"/>
       <c r="Q31" s="35"/>
       <c r="R31" s="68" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T31" s="52"/>
     </row>
-    <row r="32" spans="2:20">
+    <row r="32" spans="2:20" ht="41.65">
       <c r="B32" s="101" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>149</v>
       </c>
       <c r="D32" s="6">
@@ -4385,14 +4403,14 @@
       <c r="P32" s="35"/>
       <c r="Q32" s="35"/>
       <c r="R32" s="68" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" ht="41.65">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18">
       <c r="B33" s="101" t="s">
-        <v>114</v>
-      </c>
-      <c r="C33" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>149</v>
       </c>
       <c r="D33" s="6">
@@ -4424,12 +4442,12 @@
       <c r="P33" s="35"/>
       <c r="Q33" s="35"/>
       <c r="R33" s="68" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" ht="27.75">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" ht="41.65">
       <c r="B34" s="101" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>149</v>
@@ -4452,12 +4470,10 @@
       <c r="I34" s="20">
         <v>7</v>
       </c>
-      <c r="J34" s="20">
+      <c r="J34" s="6">
         <v>8</v>
       </c>
-      <c r="K34" s="1">
-        <v>9</v>
-      </c>
+      <c r="K34" s="35"/>
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
       <c r="N34" s="35"/>
@@ -4465,12 +4481,12 @@
       <c r="P34" s="35"/>
       <c r="Q34" s="35"/>
       <c r="R34" s="68" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="35" spans="2:18">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" ht="27.75">
       <c r="B35" s="101" t="s">
-        <v>190</v>
+        <v>113</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>149</v>
@@ -4490,40 +4506,28 @@
       <c r="H35" s="6">
         <v>6</v>
       </c>
-      <c r="I35" s="6">
+      <c r="I35" s="20">
         <v>7</v>
       </c>
-      <c r="J35" s="19">
+      <c r="J35" s="20">
         <v>8</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="1">
         <v>9</v>
       </c>
-      <c r="L35" s="21">
-        <v>10</v>
-      </c>
-      <c r="M35" s="6">
-        <v>11</v>
-      </c>
-      <c r="N35" s="6">
-        <v>12</v>
-      </c>
-      <c r="O35" s="6">
-        <v>13</v>
-      </c>
-      <c r="P35" s="6">
-        <v>14</v>
-      </c>
-      <c r="Q35" s="20">
-        <v>15</v>
-      </c>
-      <c r="R35" s="71" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="36" spans="2:18" ht="41.65">
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35"/>
+      <c r="Q35" s="35"/>
+      <c r="R35" s="68" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18">
       <c r="B36" s="101" t="s">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>149</v>
@@ -4570,15 +4574,15 @@
       <c r="Q36" s="20">
         <v>15</v>
       </c>
-      <c r="R36" s="68" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18">
+      <c r="R36" s="71" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" ht="41.65">
       <c r="B37" s="101" t="s">
-        <v>111</v>
-      </c>
-      <c r="C37" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>149</v>
       </c>
       <c r="D37" s="6">
@@ -4599,13 +4603,13 @@
       <c r="I37" s="6">
         <v>7</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37" s="19">
         <v>8</v>
       </c>
-      <c r="K37" s="12">
+      <c r="K37" s="6">
         <v>9</v>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="21">
         <v>10</v>
       </c>
       <c r="M37" s="6">
@@ -4623,15 +4627,15 @@
       <c r="Q37" s="20">
         <v>15</v>
       </c>
-      <c r="R37" s="71" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="38" spans="2:18" ht="41.65">
+      <c r="R37" s="68" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18">
       <c r="B38" s="101" t="s">
-        <v>110</v>
-      </c>
-      <c r="C38" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>149</v>
       </c>
       <c r="D38" s="6">
@@ -4655,7 +4659,7 @@
       <c r="J38" s="6">
         <v>8</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="12">
         <v>9</v>
       </c>
       <c r="L38" s="6">
@@ -4676,15 +4680,15 @@
       <c r="Q38" s="20">
         <v>15</v>
       </c>
-      <c r="R38" s="68" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18">
+      <c r="R38" s="71" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" ht="41.65">
       <c r="B39" s="101" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>149</v>
       </c>
       <c r="D39" s="6">
@@ -4729,13 +4733,13 @@
       <c r="Q39" s="20">
         <v>15</v>
       </c>
-      <c r="R39" s="71" t="s">
-        <v>233</v>
+      <c r="R39" s="68" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="2:18">
       <c r="B40" s="101" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>149</v>
@@ -4783,12 +4787,12 @@
         <v>15</v>
       </c>
       <c r="R40" s="71" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="2:18">
       <c r="B41" s="101" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>149</v>
@@ -4836,314 +4840,324 @@
         <v>15</v>
       </c>
       <c r="R41" s="71" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="2:18">
       <c r="B42" s="101" t="s">
+        <v>107</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D42" s="6">
+        <v>2</v>
+      </c>
+      <c r="E42" s="6">
+        <v>3</v>
+      </c>
+      <c r="F42" s="6">
+        <v>4</v>
+      </c>
+      <c r="G42" s="6">
+        <v>5</v>
+      </c>
+      <c r="H42" s="6">
+        <v>6</v>
+      </c>
+      <c r="I42" s="6">
+        <v>7</v>
+      </c>
+      <c r="J42" s="6">
+        <v>8</v>
+      </c>
+      <c r="K42" s="6">
+        <v>9</v>
+      </c>
+      <c r="L42" s="6">
+        <v>10</v>
+      </c>
+      <c r="M42" s="6">
+        <v>11</v>
+      </c>
+      <c r="N42" s="6">
+        <v>12</v>
+      </c>
+      <c r="O42" s="6">
+        <v>13</v>
+      </c>
+      <c r="P42" s="6">
+        <v>14</v>
+      </c>
+      <c r="Q42" s="20">
+        <v>15</v>
+      </c>
+      <c r="R42" s="71" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18">
+      <c r="B43" s="101" t="s">
         <v>106</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C43" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D42" s="22">
+      <c r="D43" s="22">
         <v>0.04</v>
       </c>
-      <c r="E42" s="22">
+      <c r="E43" s="22">
         <v>0.06</v>
       </c>
-      <c r="F42" s="22">
+      <c r="F43" s="22">
         <v>0.08</v>
       </c>
-      <c r="G42" s="22">
+      <c r="G43" s="22">
         <v>0.1</v>
       </c>
-      <c r="H42" s="22">
+      <c r="H43" s="22">
         <v>0.12</v>
       </c>
-      <c r="I42" s="22">
+      <c r="I43" s="22">
         <v>0.14000000000000001</v>
       </c>
-      <c r="J42" s="22">
+      <c r="J43" s="22">
         <v>0.16</v>
       </c>
-      <c r="K42" s="22">
+      <c r="K43" s="22">
         <v>0.18</v>
       </c>
-      <c r="L42" s="22">
+      <c r="L43" s="22">
         <v>0.2</v>
       </c>
-      <c r="M42" s="22">
+      <c r="M43" s="22">
         <v>0.22</v>
       </c>
-      <c r="N42" s="22">
+      <c r="N43" s="22">
         <v>0.24</v>
       </c>
-      <c r="O42" s="22">
+      <c r="O43" s="22">
         <v>0.26</v>
       </c>
-      <c r="P42" s="22">
+      <c r="P43" s="22">
         <v>0.28000000000000003</v>
       </c>
-      <c r="Q42" s="25">
+      <c r="Q43" s="25">
         <v>0.3</v>
-      </c>
-      <c r="R42" s="71" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18">
-      <c r="B43" s="102" t="s">
-        <v>105</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D43" s="8">
-        <v>0.06</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.09</v>
-      </c>
-      <c r="F43" s="8">
-        <v>0.12</v>
-      </c>
-      <c r="G43" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="H43" s="8">
-        <v>0.18</v>
-      </c>
-      <c r="I43" s="8">
-        <v>0.21</v>
-      </c>
-      <c r="J43" s="8">
-        <v>0.24</v>
-      </c>
-      <c r="K43" s="8">
-        <v>0.27</v>
-      </c>
-      <c r="L43" s="8">
-        <v>0.3</v>
-      </c>
-      <c r="M43" s="8">
-        <v>0.32</v>
-      </c>
-      <c r="N43" s="8">
-        <v>0.34</v>
-      </c>
-      <c r="O43" s="8">
-        <v>0.36</v>
-      </c>
-      <c r="P43" s="8">
-        <v>0.38</v>
-      </c>
-      <c r="Q43" s="70">
-        <v>0.4</v>
       </c>
       <c r="R43" s="71" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="44" spans="2:18" ht="14.65" thickBot="1">
-      <c r="B44" s="103" t="s">
+    <row r="44" spans="2:18">
+      <c r="B44" s="102" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D44" s="8">
+        <v>0.06</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.09</v>
+      </c>
+      <c r="F44" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="G44" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="H44" s="8">
+        <v>0.18</v>
+      </c>
+      <c r="I44" s="8">
+        <v>0.21</v>
+      </c>
+      <c r="J44" s="8">
+        <v>0.24</v>
+      </c>
+      <c r="K44" s="8">
+        <v>0.27</v>
+      </c>
+      <c r="L44" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="M44" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="N44" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="O44" s="8">
+        <v>0.36</v>
+      </c>
+      <c r="P44" s="8">
+        <v>0.38</v>
+      </c>
+      <c r="Q44" s="70">
+        <v>0.4</v>
+      </c>
+      <c r="R44" s="71" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" ht="14.65" thickBot="1">
+      <c r="B45" s="103" t="s">
         <v>191</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C45" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="D44" s="18">
+      <c r="D45" s="18">
         <v>2</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E45" s="18">
         <v>3</v>
       </c>
-      <c r="F44" s="18">
+      <c r="F45" s="18">
         <v>4</v>
       </c>
-      <c r="G44" s="18">
+      <c r="G45" s="18">
         <v>5</v>
       </c>
-      <c r="H44" s="18">
+      <c r="H45" s="18">
         <v>6</v>
       </c>
-      <c r="I44" s="18">
+      <c r="I45" s="18">
         <v>7</v>
       </c>
-      <c r="J44" s="18">
+      <c r="J45" s="18">
         <v>8</v>
       </c>
-      <c r="K44" s="18">
+      <c r="K45" s="18">
         <v>9</v>
       </c>
-      <c r="L44" s="18">
+      <c r="L45" s="18">
         <v>10</v>
       </c>
-      <c r="M44" s="18">
+      <c r="M45" s="18">
         <v>11</v>
       </c>
-      <c r="N44" s="18">
+      <c r="N45" s="18">
         <v>12</v>
       </c>
-      <c r="O44" s="18">
+      <c r="O45" s="18">
         <v>13</v>
       </c>
-      <c r="P44" s="18">
+      <c r="P45" s="18">
         <v>14</v>
       </c>
-      <c r="Q44" s="67">
+      <c r="Q45" s="67">
         <v>15</v>
       </c>
-      <c r="R44" s="72" t="s">
+      <c r="R45" s="72" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="45" spans="2:18" ht="15" thickTop="1" thickBot="1">
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="2"/>
-    </row>
-    <row r="46" spans="2:18" ht="14.65" thickTop="1">
-      <c r="B46" s="36" t="s">
+    <row r="46" spans="2:18" ht="15" thickTop="1" thickBot="1">
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+    </row>
+    <row r="47" spans="2:18" ht="14.65" thickTop="1">
+      <c r="B47" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="37" t="s">
+      <c r="C47" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="37" t="s">
+      <c r="D47" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E46" s="38" t="s">
+      <c r="E47" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="F46" s="38" t="s">
+      <c r="F47" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="G46" s="38" t="s">
+      <c r="G47" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="H46" s="38" t="s">
+      <c r="H47" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="I46" s="39" t="s">
+      <c r="I47" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="J46" s="40" t="s">
+      <c r="J47" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="K46" s="40" t="s">
+      <c r="K47" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="L46" s="40" t="s">
+      <c r="L47" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="M46" s="41" t="s">
+      <c r="M47" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="N46" s="41" t="s">
+      <c r="N47" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="O46" s="41" t="s">
+      <c r="O47" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="P46" s="41" t="s">
+      <c r="P47" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="Q46" s="64" t="s">
+      <c r="Q47" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="R46" s="59" t="s">
+      <c r="R47" s="59" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="47" spans="2:18" ht="42.75">
-      <c r="B47" s="85" t="s">
+    <row r="48" spans="2:18" ht="42.75">
+      <c r="B48" s="85" t="s">
         <v>103</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="D47" s="12">
-        <v>2</v>
-      </c>
-      <c r="E47" s="12">
-        <v>3</v>
-      </c>
-      <c r="F47" s="12">
-        <v>4</v>
-      </c>
-      <c r="G47" s="19">
-        <v>5</v>
-      </c>
-      <c r="H47" s="12">
-        <v>6</v>
-      </c>
-      <c r="I47" s="12">
-        <v>7</v>
-      </c>
-      <c r="J47" s="12">
-        <v>8</v>
-      </c>
-      <c r="K47" s="12">
-        <v>9</v>
-      </c>
-      <c r="L47" s="12">
-        <v>10</v>
-      </c>
-      <c r="M47" s="35"/>
-      <c r="N47" s="35"/>
-      <c r="O47" s="35"/>
-      <c r="P47" s="35"/>
-      <c r="Q47" s="35"/>
-      <c r="R47" s="73" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" ht="42.75">
-      <c r="B48" s="86" t="s">
-        <v>102</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="12">
         <v>2</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="12">
         <v>3</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48" s="12">
         <v>4</v>
       </c>
-      <c r="G48" s="20">
+      <c r="G48" s="19">
         <v>5</v>
       </c>
-      <c r="H48" s="6">
+      <c r="H48" s="12">
         <v>6</v>
       </c>
-      <c r="I48" s="6">
+      <c r="I48" s="12">
         <v>7</v>
       </c>
-      <c r="J48" s="6">
+      <c r="J48" s="12">
         <v>8</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="12">
         <v>9</v>
       </c>
-      <c r="L48" s="6">
+      <c r="L48" s="12">
         <v>10</v>
       </c>
       <c r="M48" s="35"/>
@@ -5157,7 +5171,7 @@
     </row>
     <row r="49" spans="2:18" ht="42.75">
       <c r="B49" s="86" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>148</v>
@@ -5200,7 +5214,7 @@
     </row>
     <row r="50" spans="2:18" ht="42.75">
       <c r="B50" s="86" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>148</v>
@@ -5243,7 +5257,7 @@
     </row>
     <row r="51" spans="2:18" ht="42.75">
       <c r="B51" s="86" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>148</v>
@@ -5286,7 +5300,7 @@
     </row>
     <row r="52" spans="2:18" ht="42.75">
       <c r="B52" s="86" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>148</v>
@@ -5329,37 +5343,37 @@
     </row>
     <row r="53" spans="2:18" ht="42.75">
       <c r="B53" s="86" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>148</v>
       </c>
       <c r="D53" s="6">
+        <v>2</v>
+      </c>
+      <c r="E53" s="6">
         <v>3</v>
       </c>
-      <c r="E53" s="6">
+      <c r="F53" s="6">
+        <v>4</v>
+      </c>
+      <c r="G53" s="20">
         <v>5</v>
       </c>
-      <c r="F53" s="6">
+      <c r="H53" s="6">
+        <v>6</v>
+      </c>
+      <c r="I53" s="6">
         <v>7</v>
       </c>
-      <c r="G53" s="20">
+      <c r="J53" s="6">
+        <v>8</v>
+      </c>
+      <c r="K53" s="6">
         <v>9</v>
       </c>
-      <c r="H53" s="6">
-        <v>11</v>
-      </c>
-      <c r="I53" s="6">
-        <v>12</v>
-      </c>
-      <c r="J53" s="6">
-        <v>13</v>
-      </c>
-      <c r="K53" s="6">
-        <v>14</v>
-      </c>
       <c r="L53" s="6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M53" s="35"/>
       <c r="N53" s="35"/>
@@ -5367,12 +5381,12 @@
       <c r="P53" s="35"/>
       <c r="Q53" s="35"/>
       <c r="R53" s="73" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="54" spans="2:18" ht="42.75">
       <c r="B54" s="86" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>148</v>
@@ -5410,47 +5424,55 @@
       <c r="P54" s="35"/>
       <c r="Q54" s="35"/>
       <c r="R54" s="73" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="55" spans="2:18">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="55" spans="2:18" ht="42.75">
       <c r="B55" s="86" t="s">
-        <v>95</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>196</v>
+        <v>96</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>148</v>
       </c>
       <c r="D55" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E55" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F55" s="6">
-        <v>8</v>
-      </c>
-      <c r="G55" s="6">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="G55" s="20">
+        <v>9</v>
       </c>
       <c r="H55" s="6">
         <v>11</v>
       </c>
-      <c r="I55" s="35"/>
-      <c r="J55" s="35"/>
-      <c r="K55" s="35"/>
-      <c r="L55" s="35"/>
+      <c r="I55" s="6">
+        <v>12</v>
+      </c>
+      <c r="J55" s="6">
+        <v>13</v>
+      </c>
+      <c r="K55" s="6">
+        <v>14</v>
+      </c>
+      <c r="L55" s="6">
+        <v>15</v>
+      </c>
       <c r="M55" s="35"/>
       <c r="N55" s="35"/>
       <c r="O55" s="35"/>
       <c r="P55" s="35"/>
       <c r="Q55" s="35"/>
-      <c r="R55" s="71" t="s">
-        <v>277</v>
+      <c r="R55" s="73" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="56" spans="2:18">
       <c r="B56" s="86" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>196</v>
@@ -5480,15 +5502,15 @@
       <c r="P56" s="35"/>
       <c r="Q56" s="35"/>
       <c r="R56" s="71" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="2:18">
       <c r="B57" s="86" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D57" s="6">
         <v>4</v>
@@ -5515,190 +5537,182 @@
       <c r="P57" s="35"/>
       <c r="Q57" s="35"/>
       <c r="R57" s="71" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="58" spans="2:18">
+      <c r="B58" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D58" s="6">
+        <v>4</v>
+      </c>
+      <c r="E58" s="6">
+        <v>6</v>
+      </c>
+      <c r="F58" s="6">
+        <v>8</v>
+      </c>
+      <c r="G58" s="6">
+        <v>10</v>
+      </c>
+      <c r="H58" s="6">
+        <v>11</v>
+      </c>
+      <c r="I58" s="35"/>
+      <c r="J58" s="35"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="35"/>
+      <c r="M58" s="35"/>
+      <c r="N58" s="35"/>
+      <c r="O58" s="35"/>
+      <c r="P58" s="35"/>
+      <c r="Q58" s="35"/>
+      <c r="R58" s="71" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="58" spans="2:18" ht="14.65" thickBot="1">
-      <c r="B58" s="87" t="s">
+    <row r="59" spans="2:18" ht="14.65" thickBot="1">
+      <c r="B59" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="C59" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="D58" s="18">
+      <c r="D59" s="18">
         <v>4</v>
       </c>
-      <c r="E58" s="18">
+      <c r="E59" s="18">
         <v>6</v>
       </c>
-      <c r="F58" s="18">
+      <c r="F59" s="18">
         <v>8</v>
       </c>
-      <c r="G58" s="18">
+      <c r="G59" s="18">
         <v>10</v>
       </c>
-      <c r="H58" s="18">
+      <c r="H59" s="18">
         <v>11</v>
       </c>
-      <c r="I58" s="48"/>
-      <c r="J58" s="48"/>
-      <c r="K58" s="48"/>
-      <c r="L58" s="48"/>
-      <c r="M58" s="48"/>
-      <c r="N58" s="48"/>
-      <c r="O58" s="48"/>
-      <c r="P58" s="48"/>
-      <c r="Q58" s="48"/>
-      <c r="R58" s="72" t="s">
+      <c r="I59" s="48"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48"/>
+      <c r="L59" s="48"/>
+      <c r="M59" s="48"/>
+      <c r="N59" s="48"/>
+      <c r="O59" s="48"/>
+      <c r="P59" s="48"/>
+      <c r="Q59" s="48"/>
+      <c r="R59" s="72" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="59" spans="2:18" ht="15" thickTop="1" thickBot="1">
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2"/>
-      <c r="Q59" s="2"/>
-    </row>
-    <row r="60" spans="2:18" ht="14.65" thickTop="1">
-      <c r="B60" s="36" t="s">
+    <row r="60" spans="2:18" ht="15" thickTop="1" thickBot="1">
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+    </row>
+    <row r="61" spans="2:18" ht="14.65" thickTop="1">
+      <c r="B61" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="C60" s="37" t="s">
+      <c r="C61" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D60" s="37" t="s">
+      <c r="D61" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E60" s="38" t="s">
+      <c r="E61" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="F60" s="38" t="s">
+      <c r="F61" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="G60" s="38" t="s">
+      <c r="G61" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="H60" s="38" t="s">
+      <c r="H61" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="I60" s="39" t="s">
+      <c r="I61" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="J60" s="40" t="s">
+      <c r="J61" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="K60" s="40" t="s">
+      <c r="K61" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="L60" s="40" t="s">
+      <c r="L61" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="M60" s="41" t="s">
+      <c r="M61" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="N60" s="41" t="s">
+      <c r="N61" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="O60" s="41" t="s">
+      <c r="O61" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="P60" s="41" t="s">
+      <c r="P61" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="Q60" s="64" t="s">
+      <c r="Q61" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="R60" s="59" t="s">
+      <c r="R61" s="59" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="61" spans="2:18" ht="28.5">
-      <c r="B61" s="93" t="s">
+    <row r="62" spans="2:18" ht="28.5">
+      <c r="B62" s="93" t="s">
         <v>90</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D61" s="12">
-        <v>2</v>
-      </c>
-      <c r="E61" s="12">
-        <v>3</v>
-      </c>
-      <c r="F61" s="12">
-        <v>4</v>
-      </c>
-      <c r="G61" s="12">
-        <v>5</v>
-      </c>
-      <c r="H61" s="12">
-        <v>6</v>
-      </c>
-      <c r="I61" s="12">
-        <v>7</v>
-      </c>
-      <c r="J61" s="12">
-        <v>8</v>
-      </c>
-      <c r="K61" s="12">
-        <v>9</v>
-      </c>
-      <c r="L61" s="12">
-        <v>11</v>
-      </c>
-      <c r="M61" s="35"/>
-      <c r="N61" s="35"/>
-      <c r="O61" s="35"/>
-      <c r="P61" s="35"/>
-      <c r="Q61" s="35"/>
-      <c r="R61" s="73" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="62" spans="2:18" ht="28.5">
-      <c r="B62" s="94" t="s">
-        <v>89</v>
       </c>
       <c r="C62" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D62" s="12">
         <v>2</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E62" s="12">
         <v>3</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F62" s="12">
         <v>4</v>
       </c>
-      <c r="G62" s="6">
+      <c r="G62" s="12">
         <v>5</v>
       </c>
-      <c r="H62" s="6">
+      <c r="H62" s="12">
         <v>6</v>
       </c>
-      <c r="I62" s="6">
+      <c r="I62" s="12">
         <v>7</v>
       </c>
-      <c r="J62" s="6">
+      <c r="J62" s="12">
         <v>8</v>
       </c>
-      <c r="K62" s="6">
+      <c r="K62" s="12">
         <v>9</v>
       </c>
-      <c r="L62" s="6">
+      <c r="L62" s="12">
         <v>11</v>
       </c>
       <c r="M62" s="35"/>
@@ -5712,7 +5726,7 @@
     </row>
     <row r="63" spans="2:18" ht="28.5">
       <c r="B63" s="94" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>146</v>
@@ -5755,7 +5769,7 @@
     </row>
     <row r="64" spans="2:18" ht="28.5">
       <c r="B64" s="94" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>146</v>
@@ -5798,7 +5812,7 @@
     </row>
     <row r="65" spans="2:18" ht="28.5">
       <c r="B65" s="94" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>146</v>
@@ -5841,7 +5855,7 @@
     </row>
     <row r="66" spans="2:18" ht="28.5">
       <c r="B66" s="94" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>146</v>
@@ -5884,7 +5898,7 @@
     </row>
     <row r="67" spans="2:18" ht="28.5">
       <c r="B67" s="94" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>146</v>
@@ -5925,11 +5939,11 @@
         <v>230</v>
       </c>
     </row>
-    <row r="68" spans="2:18">
+    <row r="68" spans="2:18" ht="28.5">
       <c r="B68" s="94" t="s">
-        <v>83</v>
-      </c>
-      <c r="C68" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C68" s="12" t="s">
         <v>146</v>
       </c>
       <c r="D68" s="6">
@@ -5964,13 +5978,13 @@
       <c r="O68" s="35"/>
       <c r="P68" s="35"/>
       <c r="Q68" s="35"/>
-      <c r="R68" s="71" t="s">
-        <v>223</v>
+      <c r="R68" s="73" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="69" spans="2:18">
       <c r="B69" s="94" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>146</v>
@@ -6013,7 +6027,7 @@
     </row>
     <row r="70" spans="2:18">
       <c r="B70" s="94" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>146</v>
@@ -6051,12 +6065,12 @@
       <c r="P70" s="35"/>
       <c r="Q70" s="35"/>
       <c r="R70" s="71" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71" spans="2:18">
       <c r="B71" s="94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>146</v>
@@ -6094,12 +6108,12 @@
       <c r="P71" s="35"/>
       <c r="Q71" s="35"/>
       <c r="R71" s="71" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
     </row>
     <row r="72" spans="2:18">
       <c r="B72" s="94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>146</v>
@@ -6142,7 +6156,7 @@
     </row>
     <row r="73" spans="2:18">
       <c r="B73" s="94" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>146</v>
@@ -6180,12 +6194,12 @@
       <c r="P73" s="35"/>
       <c r="Q73" s="35"/>
       <c r="R73" s="71" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="74" spans="2:18">
       <c r="B74" s="94" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>146</v>
@@ -6223,12 +6237,12 @@
       <c r="P74" s="35"/>
       <c r="Q74" s="35"/>
       <c r="R74" s="71" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="75" spans="2:18">
       <c r="B75" s="94" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>146</v>
@@ -6266,12 +6280,12 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="35"/>
       <c r="R75" s="71" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="76" spans="2:18">
       <c r="B76" s="94" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>146</v>
@@ -6309,12 +6323,12 @@
       <c r="P76" s="35"/>
       <c r="Q76" s="35"/>
       <c r="R76" s="71" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77" spans="2:18">
       <c r="B77" s="94" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>146</v>
@@ -6357,7 +6371,7 @@
     </row>
     <row r="78" spans="2:18">
       <c r="B78" s="94" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>146</v>
@@ -6400,10 +6414,10 @@
     </row>
     <row r="79" spans="2:18">
       <c r="B79" s="94" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>235</v>
+        <v>146</v>
       </c>
       <c r="D79" s="6">
         <v>2</v>
@@ -6443,10 +6457,10 @@
     </row>
     <row r="80" spans="2:18">
       <c r="B80" s="94" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>146</v>
+        <v>235</v>
       </c>
       <c r="D80" s="6">
         <v>2</v>
@@ -6486,7 +6500,7 @@
     </row>
     <row r="81" spans="2:18">
       <c r="B81" s="94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>146</v>
@@ -6524,12 +6538,12 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
       <c r="R81" s="71" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" spans="2:18">
       <c r="B82" s="94" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>146</v>
@@ -6572,7 +6586,7 @@
     </row>
     <row r="83" spans="2:18">
       <c r="B83" s="94" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>146</v>
@@ -6615,7 +6629,7 @@
     </row>
     <row r="84" spans="2:18">
       <c r="B84" s="94" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>146</v>
@@ -6656,12 +6670,12 @@
         <v>215</v>
       </c>
     </row>
-    <row r="85" spans="2:18" ht="28.5">
+    <row r="85" spans="2:18">
       <c r="B85" s="94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D85" s="6">
         <v>2</v>
@@ -6695,42 +6709,42 @@
       <c r="O85" s="35"/>
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
-      <c r="R85" s="73" t="s">
-        <v>230</v>
+      <c r="R85" s="71" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="86" spans="2:18" ht="28.5">
       <c r="B86" s="94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D86" s="13">
+      <c r="D86" s="6">
         <v>2</v>
       </c>
-      <c r="E86" s="13">
+      <c r="E86" s="6">
         <v>3</v>
       </c>
-      <c r="F86" s="13">
+      <c r="F86" s="6">
         <v>4</v>
       </c>
-      <c r="G86" s="13">
+      <c r="G86" s="6">
         <v>5</v>
       </c>
-      <c r="H86" s="13">
+      <c r="H86" s="6">
         <v>6</v>
       </c>
-      <c r="I86" s="13">
+      <c r="I86" s="6">
         <v>7</v>
       </c>
-      <c r="J86" s="13">
+      <c r="J86" s="6">
         <v>8</v>
       </c>
-      <c r="K86" s="13">
+      <c r="K86" s="6">
         <v>9</v>
       </c>
-      <c r="L86" s="13">
+      <c r="L86" s="6">
         <v>11</v>
       </c>
       <c r="M86" s="35"/>
@@ -6743,37 +6757,37 @@
       </c>
     </row>
     <row r="87" spans="2:18" ht="28.5">
-      <c r="B87" s="95" t="s">
-        <v>64</v>
+      <c r="B87" s="94" t="s">
+        <v>65</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D87" s="14">
+      <c r="D87" s="13">
         <v>2</v>
       </c>
-      <c r="E87" s="14">
+      <c r="E87" s="13">
         <v>3</v>
       </c>
-      <c r="F87" s="14">
+      <c r="F87" s="13">
         <v>4</v>
       </c>
-      <c r="G87" s="14">
+      <c r="G87" s="13">
         <v>5</v>
       </c>
-      <c r="H87" s="14">
+      <c r="H87" s="13">
         <v>6</v>
       </c>
-      <c r="I87" s="14">
+      <c r="I87" s="13">
         <v>7</v>
       </c>
-      <c r="J87" s="14">
+      <c r="J87" s="13">
         <v>8</v>
       </c>
-      <c r="K87" s="14">
+      <c r="K87" s="13">
         <v>9</v>
       </c>
-      <c r="L87" s="14">
+      <c r="L87" s="13">
         <v>11</v>
       </c>
       <c r="M87" s="35"/>
@@ -6785,11 +6799,11 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="2:18">
-      <c r="B88" s="94" t="s">
-        <v>63</v>
-      </c>
-      <c r="C88" s="15" t="s">
+    <row r="88" spans="2:18" ht="28.5">
+      <c r="B88" s="95" t="s">
+        <v>64</v>
+      </c>
+      <c r="C88" s="6" t="s">
         <v>147</v>
       </c>
       <c r="D88" s="14">
@@ -6816,7 +6830,7 @@
       <c r="K88" s="14">
         <v>9</v>
       </c>
-      <c r="L88" s="16">
+      <c r="L88" s="14">
         <v>11</v>
       </c>
       <c r="M88" s="35"/>
@@ -6824,42 +6838,42 @@
       <c r="O88" s="35"/>
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
-      <c r="R88" s="71" t="s">
-        <v>216</v>
+      <c r="R88" s="73" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="89" spans="2:18">
       <c r="B89" s="94" t="s">
-        <v>62</v>
-      </c>
-      <c r="C89" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C89" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="D89" s="17">
+      <c r="D89" s="14">
         <v>2</v>
       </c>
-      <c r="E89" s="17">
+      <c r="E89" s="14">
         <v>3</v>
       </c>
-      <c r="F89" s="17">
+      <c r="F89" s="14">
         <v>4</v>
       </c>
-      <c r="G89" s="17">
+      <c r="G89" s="14">
         <v>5</v>
       </c>
-      <c r="H89" s="17">
+      <c r="H89" s="14">
         <v>6</v>
       </c>
-      <c r="I89" s="17">
+      <c r="I89" s="14">
         <v>7</v>
       </c>
-      <c r="J89" s="17">
+      <c r="J89" s="14">
         <v>8</v>
       </c>
-      <c r="K89" s="17">
+      <c r="K89" s="14">
         <v>9</v>
       </c>
-      <c r="L89" s="17">
+      <c r="L89" s="16">
         <v>11</v>
       </c>
       <c r="M89" s="35"/>
@@ -6872,37 +6886,37 @@
       </c>
     </row>
     <row r="90" spans="2:18">
-      <c r="B90" s="95" t="s">
-        <v>61</v>
-      </c>
-      <c r="C90" s="13" t="s">
+      <c r="B90" s="94" t="s">
+        <v>62</v>
+      </c>
+      <c r="C90" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D90" s="13">
+      <c r="D90" s="17">
         <v>2</v>
       </c>
-      <c r="E90" s="13">
+      <c r="E90" s="17">
         <v>3</v>
       </c>
-      <c r="F90" s="13">
+      <c r="F90" s="17">
         <v>4</v>
       </c>
-      <c r="G90" s="13">
+      <c r="G90" s="17">
         <v>5</v>
       </c>
-      <c r="H90" s="13">
+      <c r="H90" s="17">
         <v>6</v>
       </c>
-      <c r="I90" s="13">
+      <c r="I90" s="17">
         <v>7</v>
       </c>
-      <c r="J90" s="13">
+      <c r="J90" s="17">
         <v>8</v>
       </c>
-      <c r="K90" s="13">
+      <c r="K90" s="17">
         <v>9</v>
       </c>
-      <c r="L90" s="13">
+      <c r="L90" s="17">
         <v>11</v>
       </c>
       <c r="M90" s="35"/>
@@ -6911,12 +6925,12 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
       <c r="R90" s="71" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="2:18">
       <c r="B91" s="95" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C91" s="13" t="s">
         <v>147</v>
@@ -6959,7 +6973,7 @@
     </row>
     <row r="92" spans="2:18">
       <c r="B92" s="95" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C92" s="13" t="s">
         <v>147</v>
@@ -6997,15 +7011,15 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
       <c r="R92" s="71" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
     </row>
     <row r="93" spans="2:18">
       <c r="B93" s="95" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="D93" s="13">
         <v>2</v>
@@ -7040,12 +7054,12 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
       <c r="R93" s="71" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
     </row>
     <row r="94" spans="2:18">
       <c r="B94" s="95" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C94" s="13" t="s">
         <v>56</v>
@@ -7083,12 +7097,12 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
       <c r="R94" s="71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="95" spans="2:18">
       <c r="B95" s="95" t="s">
-        <v>203</v>
+        <v>57</v>
       </c>
       <c r="C95" s="13" t="s">
         <v>56</v>
@@ -7126,15 +7140,15 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
       <c r="R95" s="71" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
     </row>
     <row r="96" spans="2:18">
       <c r="B96" s="95" t="s">
-        <v>55</v>
-      </c>
-      <c r="C96" s="17" t="s">
-        <v>146</v>
+        <v>203</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="D96" s="13">
         <v>2</v>
@@ -7169,178 +7183,178 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
       <c r="R96" s="71" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="97" spans="2:18">
+      <c r="B97" s="95" t="s">
+        <v>55</v>
+      </c>
+      <c r="C97" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D97" s="13">
+        <v>2</v>
+      </c>
+      <c r="E97" s="13">
+        <v>3</v>
+      </c>
+      <c r="F97" s="13">
+        <v>4</v>
+      </c>
+      <c r="G97" s="13">
+        <v>5</v>
+      </c>
+      <c r="H97" s="13">
+        <v>6</v>
+      </c>
+      <c r="I97" s="13">
+        <v>7</v>
+      </c>
+      <c r="J97" s="13">
+        <v>8</v>
+      </c>
+      <c r="K97" s="13">
+        <v>9</v>
+      </c>
+      <c r="L97" s="13">
+        <v>11</v>
+      </c>
+      <c r="M97" s="35"/>
+      <c r="N97" s="35"/>
+      <c r="O97" s="35"/>
+      <c r="P97" s="35"/>
+      <c r="Q97" s="35"/>
+      <c r="R97" s="71" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="97" spans="2:18" ht="14.65" thickBot="1">
-      <c r="B97" s="96" t="s">
+    <row r="98" spans="2:18" ht="14.65" thickBot="1">
+      <c r="B98" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="C97" s="18" t="s">
+      <c r="C98" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D97" s="18">
+      <c r="D98" s="18">
         <v>2</v>
       </c>
-      <c r="E97" s="18">
+      <c r="E98" s="18">
         <v>3</v>
       </c>
-      <c r="F97" s="18">
+      <c r="F98" s="18">
         <v>4</v>
       </c>
-      <c r="G97" s="18">
+      <c r="G98" s="18">
         <v>5</v>
       </c>
-      <c r="H97" s="18">
+      <c r="H98" s="18">
         <v>6</v>
       </c>
-      <c r="I97" s="18">
+      <c r="I98" s="18">
         <v>7</v>
       </c>
-      <c r="J97" s="18">
+      <c r="J98" s="18">
         <v>8</v>
       </c>
-      <c r="K97" s="18">
+      <c r="K98" s="18">
         <v>9</v>
       </c>
-      <c r="L97" s="18">
+      <c r="L98" s="18">
         <v>11</v>
       </c>
-      <c r="M97" s="48"/>
-      <c r="N97" s="48"/>
-      <c r="O97" s="48"/>
-      <c r="P97" s="48"/>
-      <c r="Q97" s="48"/>
-      <c r="R97" s="72" t="s">
+      <c r="M98" s="48"/>
+      <c r="N98" s="48"/>
+      <c r="O98" s="48"/>
+      <c r="P98" s="48"/>
+      <c r="Q98" s="48"/>
+      <c r="R98" s="72" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="98" spans="2:18" ht="15" thickTop="1" thickBot="1"/>
-    <row r="99" spans="2:18" ht="14.65" thickTop="1">
-      <c r="B99" s="36" t="s">
+    <row r="99" spans="2:18" ht="15" thickTop="1" thickBot="1"/>
+    <row r="100" spans="2:18" ht="14.65" thickTop="1">
+      <c r="B100" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C99" s="37" t="s">
+      <c r="C100" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D99" s="37" t="s">
+      <c r="D100" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E99" s="38" t="s">
+      <c r="E100" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="F99" s="38" t="s">
+      <c r="F100" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="G99" s="38" t="s">
+      <c r="G100" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="H99" s="38" t="s">
+      <c r="H100" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="I99" s="39" t="s">
+      <c r="I100" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="J99" s="40" t="s">
+      <c r="J100" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="K99" s="40" t="s">
+      <c r="K100" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="L99" s="40" t="s">
+      <c r="L100" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="M99" s="41" t="s">
+      <c r="M100" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="N99" s="41" t="s">
+      <c r="N100" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="O99" s="41" t="s">
+      <c r="O100" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="P99" s="41" t="s">
+      <c r="P100" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="Q99" s="64" t="s">
+      <c r="Q100" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="R99" s="59" t="s">
+      <c r="R100" s="59" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="100" spans="2:18" ht="42.75">
-      <c r="B100" s="97" t="s">
+    <row r="101" spans="2:18" ht="42.75">
+      <c r="B101" s="97" t="s">
         <v>52</v>
       </c>
-      <c r="C100" s="12" t="s">
+      <c r="C101" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="D100" s="23">
+      <c r="D101" s="23">
         <v>0.18</v>
       </c>
-      <c r="E100" s="23">
+      <c r="E101" s="23">
         <v>0.27</v>
       </c>
-      <c r="F100" s="23">
+      <c r="F101" s="23">
         <v>0.36</v>
       </c>
-      <c r="G100" s="23">
+      <c r="G101" s="23">
         <v>0.45</v>
       </c>
-      <c r="H100" s="23">
+      <c r="H101" s="23">
         <v>0.54</v>
       </c>
-      <c r="I100" s="23">
+      <c r="I101" s="23">
         <v>0.63</v>
       </c>
-      <c r="J100" s="23">
+      <c r="J101" s="23">
         <v>0.72</v>
       </c>
-      <c r="K100" s="24">
-        <v>0.81</v>
-      </c>
-      <c r="L100" s="23">
-        <v>1</v>
-      </c>
-      <c r="M100" s="35"/>
-      <c r="N100" s="35"/>
-      <c r="O100" s="35"/>
-      <c r="P100" s="35"/>
-      <c r="Q100" s="35"/>
-      <c r="R100" s="73" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="101" spans="2:18">
-      <c r="B101" s="98" t="s">
-        <v>51</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D101" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="E101" s="22">
-        <v>0.27</v>
-      </c>
-      <c r="F101" s="22">
-        <v>0.36</v>
-      </c>
-      <c r="G101" s="22">
-        <v>0.45</v>
-      </c>
-      <c r="H101" s="22">
-        <v>0.54</v>
-      </c>
-      <c r="I101" s="22">
-        <v>0.63</v>
-      </c>
-      <c r="J101" s="22">
-        <v>0.72</v>
-      </c>
-      <c r="K101" s="25">
+      <c r="K101" s="24">
         <v>0.81</v>
       </c>
       <c r="L101" s="23">
@@ -7351,36 +7365,36 @@
       <c r="O101" s="35"/>
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
-      <c r="R101" s="71" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="102" spans="2:18" ht="42.75">
+      <c r="R101" s="73" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="102" spans="2:18">
       <c r="B102" s="98" t="s">
-        <v>50</v>
-      </c>
-      <c r="C102" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C102" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D102" s="23">
+      <c r="D102" s="22">
         <v>0.18</v>
       </c>
-      <c r="E102" s="23">
+      <c r="E102" s="22">
         <v>0.27</v>
       </c>
-      <c r="F102" s="23">
+      <c r="F102" s="22">
         <v>0.36</v>
       </c>
-      <c r="G102" s="23">
+      <c r="G102" s="22">
         <v>0.45</v>
       </c>
-      <c r="H102" s="23">
+      <c r="H102" s="22">
         <v>0.54</v>
       </c>
-      <c r="I102" s="23">
+      <c r="I102" s="22">
         <v>0.63</v>
       </c>
-      <c r="J102" s="23">
+      <c r="J102" s="22">
         <v>0.72</v>
       </c>
       <c r="K102" s="25">
@@ -7394,13 +7408,13 @@
       <c r="O102" s="35"/>
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
-      <c r="R102" s="73" t="s">
-        <v>253</v>
+      <c r="R102" s="71" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="103" spans="2:18" ht="42.75">
       <c r="B103" s="98" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C103" s="12" t="s">
         <v>150</v>
@@ -7438,35 +7452,35 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
       <c r="R103" s="73" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="104" spans="2:18">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="104" spans="2:18" ht="42.75">
       <c r="B104" s="98" t="s">
-        <v>48</v>
-      </c>
-      <c r="C104" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C104" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="D104" s="22">
+      <c r="D104" s="23">
         <v>0.18</v>
       </c>
-      <c r="E104" s="22">
+      <c r="E104" s="23">
         <v>0.27</v>
       </c>
-      <c r="F104" s="22">
+      <c r="F104" s="23">
         <v>0.36</v>
       </c>
-      <c r="G104" s="22">
+      <c r="G104" s="23">
         <v>0.45</v>
       </c>
-      <c r="H104" s="22">
+      <c r="H104" s="23">
         <v>0.54</v>
       </c>
-      <c r="I104" s="22">
+      <c r="I104" s="23">
         <v>0.63</v>
       </c>
-      <c r="J104" s="22">
+      <c r="J104" s="23">
         <v>0.72</v>
       </c>
       <c r="K104" s="25">
@@ -7480,322 +7494,322 @@
       <c r="O104" s="35"/>
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
-      <c r="R104" s="71" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="105" spans="2:18" ht="42.75">
+      <c r="R104" s="73" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="105" spans="2:18">
       <c r="B105" s="98" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D105" s="22">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="E105" s="22">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="F105" s="22">
-        <v>0.16</v>
+        <v>0.36</v>
       </c>
       <c r="G105" s="22">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="H105" s="22">
-        <v>0.24</v>
+        <v>0.54</v>
       </c>
       <c r="I105" s="22">
-        <v>0.28000000000000003</v>
+        <v>0.63</v>
       </c>
       <c r="J105" s="22">
-        <v>0.32</v>
+        <v>0.72</v>
       </c>
       <c r="K105" s="25">
-        <v>0.36</v>
-      </c>
-      <c r="L105" s="22">
-        <v>0.4</v>
+        <v>0.81</v>
+      </c>
+      <c r="L105" s="23">
+        <v>1</v>
       </c>
       <c r="M105" s="35"/>
       <c r="N105" s="35"/>
       <c r="O105" s="35"/>
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
-      <c r="R105" s="73" t="s">
+      <c r="R105" s="71" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="106" spans="2:18" ht="42.75">
+      <c r="B106" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D106" s="22">
+        <v>0.08</v>
+      </c>
+      <c r="E106" s="22">
+        <v>0.12</v>
+      </c>
+      <c r="F106" s="22">
+        <v>0.16</v>
+      </c>
+      <c r="G106" s="22">
+        <v>0.2</v>
+      </c>
+      <c r="H106" s="22">
+        <v>0.24</v>
+      </c>
+      <c r="I106" s="22">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J106" s="22">
+        <v>0.32</v>
+      </c>
+      <c r="K106" s="25">
+        <v>0.36</v>
+      </c>
+      <c r="L106" s="22">
+        <v>0.4</v>
+      </c>
+      <c r="M106" s="35"/>
+      <c r="N106" s="35"/>
+      <c r="O106" s="35"/>
+      <c r="P106" s="35"/>
+      <c r="Q106" s="35"/>
+      <c r="R106" s="73" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="106" spans="2:18" ht="43.15" thickBot="1">
-      <c r="B106" s="99" t="s">
+    <row r="107" spans="2:18" ht="43.15" thickBot="1">
+      <c r="B107" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="C106" s="18" t="s">
+      <c r="C107" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="D106" s="26">
+      <c r="D107" s="26">
         <v>0.18</v>
       </c>
-      <c r="E106" s="26">
+      <c r="E107" s="26">
         <v>0.27</v>
       </c>
-      <c r="F106" s="26">
+      <c r="F107" s="26">
         <v>0.36</v>
       </c>
-      <c r="G106" s="26">
+      <c r="G107" s="26">
         <v>0.45</v>
       </c>
-      <c r="H106" s="26">
+      <c r="H107" s="26">
         <v>0.54</v>
       </c>
-      <c r="I106" s="26">
+      <c r="I107" s="26">
         <v>0.63</v>
       </c>
-      <c r="J106" s="26">
+      <c r="J107" s="26">
         <v>0.72</v>
       </c>
-      <c r="K106" s="27">
+      <c r="K107" s="27">
         <v>0.81</v>
       </c>
-      <c r="L106" s="26">
+      <c r="L107" s="26">
         <v>1</v>
       </c>
-      <c r="M106" s="48"/>
-      <c r="N106" s="48"/>
-      <c r="O106" s="48"/>
-      <c r="P106" s="48"/>
-      <c r="Q106" s="48"/>
-      <c r="R106" s="74" t="s">
+      <c r="M107" s="48"/>
+      <c r="N107" s="48"/>
+      <c r="O107" s="48"/>
+      <c r="P107" s="48"/>
+      <c r="Q107" s="48"/>
+      <c r="R107" s="74" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="107" spans="2:18" ht="15" thickTop="1" thickBot="1"/>
-    <row r="108" spans="2:18" ht="14.65" thickTop="1">
-      <c r="B108" s="36" t="s">
+    <row r="108" spans="2:18" ht="15" thickTop="1" thickBot="1"/>
+    <row r="109" spans="2:18" ht="14.65" thickTop="1">
+      <c r="B109" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="C108" s="37" t="s">
+      <c r="C109" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D108" s="37" t="s">
+      <c r="D109" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E108" s="38" t="s">
+      <c r="E109" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="F108" s="38" t="s">
+      <c r="F109" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="G108" s="38" t="s">
+      <c r="G109" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="H108" s="38" t="s">
+      <c r="H109" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="I108" s="39" t="s">
+      <c r="I109" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="J108" s="40" t="s">
+      <c r="J109" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="K108" s="40" t="s">
+      <c r="K109" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="L108" s="40" t="s">
+      <c r="L109" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="M108" s="41" t="s">
+      <c r="M109" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="N108" s="41" t="s">
+      <c r="N109" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="O108" s="41" t="s">
+      <c r="O109" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="P108" s="41" t="s">
+      <c r="P109" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="Q108" s="42" t="s">
+      <c r="Q109" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="R108" s="59" t="s">
+      <c r="R109" s="59" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="109" spans="2:18" ht="42.75">
-      <c r="B109" s="88" t="s">
+    <row r="110" spans="2:18" ht="42.75">
+      <c r="B110" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="C109" s="12" t="s">
+      <c r="C110" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D109" s="12">
+      <c r="D110" s="12">
         <v>2</v>
       </c>
-      <c r="E109" s="12">
+      <c r="E110" s="12">
         <v>3</v>
       </c>
-      <c r="F109" s="12">
+      <c r="F110" s="12">
         <v>4</v>
       </c>
-      <c r="G109" s="12">
+      <c r="G110" s="12">
         <v>5</v>
       </c>
-      <c r="H109" s="12">
+      <c r="H110" s="12">
         <v>6</v>
       </c>
-      <c r="I109" s="12">
+      <c r="I110" s="12">
         <v>7</v>
       </c>
-      <c r="J109" s="12">
+      <c r="J110" s="12">
         <v>8</v>
       </c>
-      <c r="K109" s="12">
+      <c r="K110" s="12">
         <v>9</v>
       </c>
-      <c r="L109" s="12">
+      <c r="L110" s="12">
         <v>10</v>
       </c>
-      <c r="M109" s="4"/>
-      <c r="N109" s="4"/>
-      <c r="O109" s="4"/>
-      <c r="P109" s="4"/>
-      <c r="Q109" s="43"/>
-      <c r="R109" s="73" t="s">
+      <c r="M110" s="4"/>
+      <c r="N110" s="4"/>
+      <c r="O110" s="4"/>
+      <c r="P110" s="4"/>
+      <c r="Q110" s="43"/>
+      <c r="R110" s="73" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="110" spans="2:18" ht="42.75">
-      <c r="B110" s="89" t="s">
+    <row r="111" spans="2:18" ht="42.75">
+      <c r="B111" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C110" s="6" t="s">
+      <c r="C111" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D110" s="6">
+      <c r="D111" s="6">
         <v>4</v>
       </c>
-      <c r="E110" s="6">
+      <c r="E111" s="6">
         <v>6</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F111" s="6">
         <v>8</v>
       </c>
-      <c r="G110" s="6">
+      <c r="G111" s="6">
         <v>10</v>
       </c>
-      <c r="H110" s="6">
+      <c r="H111" s="6">
         <v>12</v>
       </c>
-      <c r="I110" s="6">
+      <c r="I111" s="6">
         <v>14</v>
       </c>
-      <c r="J110" s="6">
+      <c r="J111" s="6">
         <v>16</v>
       </c>
-      <c r="K110" s="6">
+      <c r="K111" s="6">
         <v>18</v>
       </c>
-      <c r="L110" s="6">
+      <c r="L111" s="6">
         <v>20</v>
       </c>
-      <c r="M110" s="6">
+      <c r="M111" s="6">
         <v>22</v>
       </c>
-      <c r="N110" s="6">
+      <c r="N111" s="6">
         <v>24</v>
       </c>
-      <c r="O110" s="6">
+      <c r="O111" s="6">
         <v>26</v>
       </c>
-      <c r="P110" s="6">
+      <c r="P111" s="6">
         <v>28</v>
       </c>
-      <c r="Q110" s="44">
+      <c r="Q111" s="44">
         <v>30</v>
       </c>
-      <c r="R110" s="73" t="s">
+      <c r="R111" s="73" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="111" spans="2:18" ht="42.75">
-      <c r="B111" s="88" t="s">
+    <row r="112" spans="2:18" ht="42.75">
+      <c r="B112" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="C111" s="12" t="s">
+      <c r="C112" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="D111" s="12">
+      <c r="D112" s="12">
         <v>2</v>
       </c>
-      <c r="E111" s="12">
+      <c r="E112" s="12">
         <v>3</v>
       </c>
-      <c r="F111" s="12">
+      <c r="F112" s="12">
         <v>4</v>
       </c>
-      <c r="G111" s="12">
+      <c r="G112" s="12">
         <v>5</v>
       </c>
-      <c r="H111" s="12">
+      <c r="H112" s="12">
         <v>6</v>
       </c>
-      <c r="I111" s="12">
+      <c r="I112" s="12">
         <v>7</v>
       </c>
-      <c r="J111" s="12">
+      <c r="J112" s="12">
         <v>8</v>
       </c>
-      <c r="K111" s="12">
+      <c r="K112" s="12">
         <v>9</v>
       </c>
-      <c r="L111" s="12">
+      <c r="L112" s="12">
         <v>10</v>
-      </c>
-      <c r="M111" s="4"/>
-      <c r="N111" s="4"/>
-      <c r="O111" s="4"/>
-      <c r="P111" s="4"/>
-      <c r="Q111" s="43"/>
-      <c r="R111" s="73" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="112" spans="2:18" ht="28.5">
-      <c r="B112" s="89" t="s">
-        <v>21</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D112" s="6">
-        <v>20</v>
-      </c>
-      <c r="E112" s="6">
-        <v>30</v>
-      </c>
-      <c r="F112" s="6">
-        <v>40</v>
-      </c>
-      <c r="G112" s="6">
-        <v>50</v>
-      </c>
-      <c r="H112" s="6">
-        <v>60</v>
-      </c>
-      <c r="I112" s="6">
-        <v>70</v>
-      </c>
-      <c r="J112" s="6">
-        <v>80</v>
-      </c>
-      <c r="K112" s="6">
-        <v>90</v>
-      </c>
-      <c r="L112" s="6">
-        <v>100</v>
       </c>
       <c r="M112" s="4"/>
       <c r="N112" s="4"/>
@@ -7803,260 +7817,250 @@
       <c r="P112" s="4"/>
       <c r="Q112" s="43"/>
       <c r="R112" s="73" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="113" spans="2:20" ht="28.5">
+      <c r="B113" s="89" t="s">
+        <v>21</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D113" s="6">
+        <v>20</v>
+      </c>
+      <c r="E113" s="6">
+        <v>30</v>
+      </c>
+      <c r="F113" s="6">
+        <v>40</v>
+      </c>
+      <c r="G113" s="6">
+        <v>50</v>
+      </c>
+      <c r="H113" s="6">
+        <v>60</v>
+      </c>
+      <c r="I113" s="6">
+        <v>70</v>
+      </c>
+      <c r="J113" s="6">
+        <v>80</v>
+      </c>
+      <c r="K113" s="6">
+        <v>90</v>
+      </c>
+      <c r="L113" s="6">
+        <v>100</v>
+      </c>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
+      <c r="P113" s="4"/>
+      <c r="Q113" s="43"/>
+      <c r="R113" s="73" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="113" spans="2:20" ht="42.75">
-      <c r="B113" s="90" t="s">
+    <row r="114" spans="2:20" ht="42.75">
+      <c r="B114" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="C113" s="7" t="s">
+      <c r="C114" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D113" s="7">
+      <c r="D114" s="7">
         <v>4</v>
       </c>
-      <c r="E113" s="7">
+      <c r="E114" s="7">
         <v>6</v>
       </c>
-      <c r="F113" s="7">
+      <c r="F114" s="7">
         <v>8</v>
       </c>
-      <c r="G113" s="7">
+      <c r="G114" s="7">
         <v>10</v>
       </c>
-      <c r="H113" s="7">
+      <c r="H114" s="7">
         <v>12</v>
       </c>
-      <c r="I113" s="7">
+      <c r="I114" s="7">
         <v>14</v>
       </c>
-      <c r="J113" s="7">
+      <c r="J114" s="7">
         <v>16</v>
       </c>
-      <c r="K113" s="7">
+      <c r="K114" s="7">
         <v>18</v>
       </c>
-      <c r="L113" s="7">
+      <c r="L114" s="7">
         <v>20</v>
       </c>
-      <c r="M113" s="5"/>
-      <c r="N113" s="5"/>
-      <c r="O113" s="5"/>
-      <c r="P113" s="5"/>
-      <c r="Q113" s="45"/>
-      <c r="R113" s="73" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="114" spans="2:20" ht="42.75">
-      <c r="B114" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="C114" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="D114" s="12">
-        <v>4</v>
-      </c>
-      <c r="E114" s="12">
-        <v>6</v>
-      </c>
-      <c r="F114" s="12">
-        <v>8</v>
-      </c>
-      <c r="G114" s="12">
-        <v>10</v>
-      </c>
-      <c r="H114" s="12">
-        <v>12</v>
-      </c>
-      <c r="I114" s="12">
-        <v>14</v>
-      </c>
-      <c r="J114" s="12">
-        <v>16</v>
-      </c>
-      <c r="K114" s="12">
-        <v>18</v>
-      </c>
-      <c r="L114" s="12">
-        <v>20</v>
-      </c>
-      <c r="M114" s="4"/>
-      <c r="N114" s="4"/>
-      <c r="O114" s="4"/>
-      <c r="P114" s="4"/>
-      <c r="Q114" s="43"/>
+      <c r="M114" s="5"/>
+      <c r="N114" s="5"/>
+      <c r="O114" s="5"/>
+      <c r="P114" s="5"/>
+      <c r="Q114" s="45"/>
       <c r="R114" s="73" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="115" spans="2:20">
-      <c r="B115" s="89" t="s">
+    <row r="115" spans="2:20" ht="42.75">
+      <c r="B115" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D115" s="12">
+        <v>4</v>
+      </c>
+      <c r="E115" s="12">
+        <v>6</v>
+      </c>
+      <c r="F115" s="12">
+        <v>8</v>
+      </c>
+      <c r="G115" s="12">
+        <v>10</v>
+      </c>
+      <c r="H115" s="12">
+        <v>12</v>
+      </c>
+      <c r="I115" s="12">
+        <v>14</v>
+      </c>
+      <c r="J115" s="12">
+        <v>16</v>
+      </c>
+      <c r="K115" s="12">
+        <v>18</v>
+      </c>
+      <c r="L115" s="12">
         <v>20</v>
       </c>
-      <c r="C115" s="6" t="s">
+      <c r="M115" s="4"/>
+      <c r="N115" s="4"/>
+      <c r="O115" s="4"/>
+      <c r="P115" s="4"/>
+      <c r="Q115" s="43"/>
+      <c r="R115" s="73" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="116" spans="2:20">
+      <c r="B116" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="C116" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D115" s="22">
+      <c r="D116" s="22">
         <v>0.08</v>
       </c>
-      <c r="E115" s="22">
+      <c r="E116" s="22">
         <v>0.12</v>
       </c>
-      <c r="F115" s="22">
+      <c r="F116" s="22">
         <v>0.16</v>
       </c>
-      <c r="G115" s="22">
+      <c r="G116" s="22">
         <v>0.2</v>
       </c>
-      <c r="H115" s="22">
+      <c r="H116" s="22">
         <v>0.24</v>
       </c>
-      <c r="I115" s="22">
+      <c r="I116" s="22">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J115" s="22">
+      <c r="J116" s="22">
         <v>0.32</v>
       </c>
-      <c r="K115" s="22">
+      <c r="K116" s="22">
         <v>0.36</v>
       </c>
-      <c r="L115" s="25">
+      <c r="L116" s="25">
         <v>0.4</v>
       </c>
-      <c r="M115" s="22">
+      <c r="M116" s="22">
         <v>0.42</v>
       </c>
-      <c r="N115" s="22">
+      <c r="N116" s="22">
         <v>0.44</v>
       </c>
-      <c r="O115" s="22">
+      <c r="O116" s="22">
         <v>0.46</v>
       </c>
-      <c r="P115" s="22">
+      <c r="P116" s="22">
         <v>0.48</v>
       </c>
-      <c r="Q115" s="46">
+      <c r="Q116" s="46">
         <v>0.5</v>
       </c>
-      <c r="R115" s="71" t="s">
+      <c r="R116" s="71" t="s">
         <v>224</v>
-      </c>
-    </row>
-    <row r="116" spans="2:20">
-      <c r="B116" s="91" t="s">
-        <v>10</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="D116" s="22">
-        <v>0.04</v>
-      </c>
-      <c r="E116" s="22">
-        <v>0.06</v>
-      </c>
-      <c r="F116" s="22">
-        <v>0.08</v>
-      </c>
-      <c r="G116" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="H116" s="22">
-        <v>0.12</v>
-      </c>
-      <c r="I116" s="22">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="J116" s="22">
-        <v>0.16</v>
-      </c>
-      <c r="K116" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="L116" s="22">
-        <v>0.2</v>
-      </c>
-      <c r="M116" s="22">
-        <v>0.22</v>
-      </c>
-      <c r="N116" s="22">
-        <v>0.24</v>
-      </c>
-      <c r="O116" s="22">
-        <v>0.26</v>
-      </c>
-      <c r="P116" s="22">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="Q116" s="46">
-        <v>0.3</v>
-      </c>
-      <c r="R116" s="71" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="117" spans="2:20">
       <c r="B117" s="91" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D117" s="22">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E117" s="22">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="F117" s="22">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="G117" s="22">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H117" s="22">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="I117" s="22">
-        <v>7.0000000000000007E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J117" s="22">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="K117" s="22">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="L117" s="22">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="M117" s="22">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="N117" s="22">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="O117" s="22">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="P117" s="22">
-        <v>0.14000000000000001</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="Q117" s="46">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="R117" s="71" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="118" spans="2:20" ht="14.65" thickBot="1">
       <c r="B118" s="91" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="D118" s="22">
         <v>0.02</v>
@@ -8106,10 +8110,10 @@
     </row>
     <row r="119" spans="2:20" ht="14.65" thickBot="1">
       <c r="B119" s="91" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D119" s="22">
         <v>0.02</v>
@@ -8159,221 +8163,231 @@
       <c r="T119" s="52"/>
     </row>
     <row r="120" spans="2:20">
-      <c r="B120" s="89" t="s">
+      <c r="B120" s="91" t="s">
+        <v>145</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D120" s="22">
+        <v>0.02</v>
+      </c>
+      <c r="E120" s="22">
+        <v>0.03</v>
+      </c>
+      <c r="F120" s="22">
+        <v>0.04</v>
+      </c>
+      <c r="G120" s="22">
+        <v>0.05</v>
+      </c>
+      <c r="H120" s="22">
+        <v>0.06</v>
+      </c>
+      <c r="I120" s="22">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J120" s="22">
+        <v>0.08</v>
+      </c>
+      <c r="K120" s="22">
+        <v>0.09</v>
+      </c>
+      <c r="L120" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="M120" s="22">
+        <v>0.11</v>
+      </c>
+      <c r="N120" s="22">
+        <v>0.12</v>
+      </c>
+      <c r="O120" s="22">
+        <v>0.13</v>
+      </c>
+      <c r="P120" s="22">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q120" s="46">
+        <v>0.15</v>
+      </c>
+      <c r="R120" s="71" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="121" spans="2:20">
+      <c r="B121" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="C120" s="6" t="s">
+      <c r="C121" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="D120" s="22">
+      <c r="D121" s="22">
         <v>0.08</v>
       </c>
-      <c r="E120" s="22">
+      <c r="E121" s="22">
         <v>0.12</v>
       </c>
-      <c r="F120" s="22">
+      <c r="F121" s="22">
         <v>0.16</v>
       </c>
-      <c r="G120" s="22">
+      <c r="G121" s="22">
         <v>0.2</v>
       </c>
-      <c r="H120" s="22">
+      <c r="H121" s="22">
         <v>0.24</v>
       </c>
-      <c r="I120" s="22">
+      <c r="I121" s="22">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J120" s="22">
+      <c r="J121" s="22">
         <v>0.32</v>
       </c>
-      <c r="K120" s="22">
+      <c r="K121" s="22">
         <v>0.36</v>
       </c>
-      <c r="L120" s="22">
+      <c r="L121" s="22">
         <v>0.4</v>
       </c>
-      <c r="M120" s="35"/>
-      <c r="N120" s="35"/>
-      <c r="O120" s="35"/>
-      <c r="P120" s="35"/>
-      <c r="Q120" s="47"/>
-      <c r="R120" s="71" t="s">
+      <c r="M121" s="35"/>
+      <c r="N121" s="35"/>
+      <c r="O121" s="35"/>
+      <c r="P121" s="35"/>
+      <c r="Q121" s="47"/>
+      <c r="R121" s="71" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="121" spans="2:20" ht="14.65" thickBot="1">
-      <c r="B121" s="92" t="s">
+    <row r="122" spans="2:20" ht="14.65" thickBot="1">
+      <c r="B122" s="92" t="s">
         <v>18</v>
       </c>
-      <c r="C121" s="18" t="s">
+      <c r="C122" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="D121" s="26">
+      <c r="D122" s="26">
         <v>0.08</v>
       </c>
-      <c r="E121" s="26">
+      <c r="E122" s="26">
         <v>0.12</v>
       </c>
-      <c r="F121" s="26">
+      <c r="F122" s="26">
         <v>0.16</v>
       </c>
-      <c r="G121" s="26">
+      <c r="G122" s="26">
         <v>0.2</v>
       </c>
-      <c r="H121" s="26">
+      <c r="H122" s="26">
         <v>0.24</v>
       </c>
-      <c r="I121" s="26">
+      <c r="I122" s="26">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J121" s="26">
+      <c r="J122" s="26">
         <v>0.32</v>
       </c>
-      <c r="K121" s="26">
+      <c r="K122" s="26">
         <v>0.36</v>
       </c>
-      <c r="L121" s="26">
+      <c r="L122" s="26">
         <v>0.4</v>
       </c>
-      <c r="M121" s="48"/>
-      <c r="N121" s="48"/>
-      <c r="O121" s="48"/>
-      <c r="P121" s="48"/>
-      <c r="Q121" s="49"/>
-      <c r="R121" s="72" t="s">
+      <c r="M122" s="48"/>
+      <c r="N122" s="48"/>
+      <c r="O122" s="48"/>
+      <c r="P122" s="48"/>
+      <c r="Q122" s="49"/>
+      <c r="R122" s="72" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="122" spans="2:20" ht="15" thickTop="1" thickBot="1"/>
-    <row r="123" spans="2:20" ht="14.65" thickTop="1">
-      <c r="B123" s="36" t="s">
+    <row r="123" spans="2:20" ht="15" thickTop="1" thickBot="1"/>
+    <row r="124" spans="2:20" ht="14.65" thickTop="1">
+      <c r="B124" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="C123" s="37" t="s">
+      <c r="C124" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D123" s="37" t="s">
+      <c r="D124" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E123" s="38" t="s">
+      <c r="E124" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="F123" s="38" t="s">
+      <c r="F124" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="G123" s="38" t="s">
+      <c r="G124" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="H123" s="38" t="s">
+      <c r="H124" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="I123" s="39" t="s">
+      <c r="I124" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="J123" s="40" t="s">
+      <c r="J124" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="K123" s="40" t="s">
+      <c r="K124" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="L123" s="40" t="s">
+      <c r="L124" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="M123" s="41" t="s">
+      <c r="M124" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="N123" s="41" t="s">
+      <c r="N124" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="O123" s="41" t="s">
+      <c r="O124" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="P123" s="41" t="s">
+      <c r="P124" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="Q123" s="42" t="s">
+      <c r="Q124" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="R123" s="59" t="s">
+      <c r="R124" s="59" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="124" spans="2:20" ht="42.75">
-      <c r="B124" s="105" t="s">
+    <row r="125" spans="2:20" ht="42.75">
+      <c r="B125" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="C124" s="6" t="s">
+      <c r="C125" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D124" s="22">
+      <c r="D125" s="22">
         <v>0.06</v>
       </c>
-      <c r="E124" s="22">
+      <c r="E125" s="22">
         <v>0.09</v>
       </c>
-      <c r="F124" s="22">
+      <c r="F125" s="22">
         <v>0.12</v>
       </c>
-      <c r="G124" s="22">
+      <c r="G125" s="22">
         <v>0.15</v>
       </c>
-      <c r="H124" s="22">
+      <c r="H125" s="22">
         <v>0.18</v>
       </c>
-      <c r="I124" s="22">
+      <c r="I125" s="22">
         <v>0.21</v>
       </c>
-      <c r="J124" s="22">
+      <c r="J125" s="22">
         <v>0.24</v>
       </c>
-      <c r="K124" s="22">
+      <c r="K125" s="22">
         <v>0.27</v>
       </c>
-      <c r="L124" s="22">
+      <c r="L125" s="22">
         <v>0.3</v>
-      </c>
-      <c r="M124" s="4"/>
-      <c r="N124" s="4"/>
-      <c r="O124" s="4"/>
-      <c r="P124" s="4"/>
-      <c r="Q124" s="43"/>
-      <c r="R124" s="63" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="125" spans="2:20" ht="28.5">
-      <c r="B125" s="105" t="s">
-        <v>22</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D125" s="22">
-        <v>0.4</v>
-      </c>
-      <c r="E125" s="22">
-        <v>0.6</v>
-      </c>
-      <c r="F125" s="22">
-        <v>0.8</v>
-      </c>
-      <c r="G125" s="22">
-        <v>1</v>
-      </c>
-      <c r="H125" s="22">
-        <v>1.2</v>
-      </c>
-      <c r="I125" s="22">
-        <v>1.4</v>
-      </c>
-      <c r="J125" s="22">
-        <v>1.6</v>
-      </c>
-      <c r="K125" s="22">
-        <v>1.8</v>
-      </c>
-      <c r="L125" s="22">
-        <v>2</v>
       </c>
       <c r="M125" s="4"/>
       <c r="N125" s="4"/>
@@ -8381,42 +8395,42 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="43"/>
       <c r="R125" s="63" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="126" spans="2:20" ht="28.5">
       <c r="B126" s="105" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="D126" s="6">
-        <v>10</v>
-      </c>
-      <c r="E126" s="6">
-        <v>15</v>
-      </c>
-      <c r="F126" s="6">
-        <v>20</v>
-      </c>
-      <c r="G126" s="6">
-        <v>25</v>
-      </c>
-      <c r="H126" s="6">
-        <v>30</v>
-      </c>
-      <c r="I126" s="6">
-        <v>35</v>
-      </c>
-      <c r="J126" s="6">
-        <v>40</v>
-      </c>
-      <c r="K126" s="6">
-        <v>45</v>
-      </c>
-      <c r="L126" s="6">
-        <v>50</v>
+        <v>161</v>
+      </c>
+      <c r="D126" s="22">
+        <v>0.4</v>
+      </c>
+      <c r="E126" s="22">
+        <v>0.6</v>
+      </c>
+      <c r="F126" s="22">
+        <v>0.8</v>
+      </c>
+      <c r="G126" s="22">
+        <v>1</v>
+      </c>
+      <c r="H126" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="I126" s="22">
+        <v>1.4</v>
+      </c>
+      <c r="J126" s="22">
+        <v>1.6</v>
+      </c>
+      <c r="K126" s="22">
+        <v>1.8</v>
+      </c>
+      <c r="L126" s="22">
+        <v>2</v>
       </c>
       <c r="M126" s="4"/>
       <c r="N126" s="4"/>
@@ -8424,91 +8438,101 @@
       <c r="P126" s="4"/>
       <c r="Q126" s="43"/>
       <c r="R126" s="63" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="127" spans="2:20">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="127" spans="2:20" ht="28.5">
       <c r="B127" s="105" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D127" s="22">
-        <v>0.02</v>
-      </c>
-      <c r="E127" s="22">
-        <v>0.03</v>
-      </c>
-      <c r="F127" s="22">
-        <v>0.04</v>
-      </c>
-      <c r="G127" s="22">
-        <v>0.05</v>
-      </c>
-      <c r="H127" s="22">
-        <v>0.06</v>
-      </c>
-      <c r="I127" s="22">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="J127" s="22">
-        <v>0.08</v>
-      </c>
-      <c r="K127" s="22">
-        <v>0.09</v>
-      </c>
-      <c r="L127" s="22">
-        <v>0.11</v>
+        <v>186</v>
+      </c>
+      <c r="D127" s="6">
+        <v>10</v>
+      </c>
+      <c r="E127" s="6">
+        <v>15</v>
+      </c>
+      <c r="F127" s="6">
+        <v>20</v>
+      </c>
+      <c r="G127" s="6">
+        <v>25</v>
+      </c>
+      <c r="H127" s="6">
+        <v>30</v>
+      </c>
+      <c r="I127" s="6">
+        <v>35</v>
+      </c>
+      <c r="J127" s="6">
+        <v>40</v>
+      </c>
+      <c r="K127" s="6">
+        <v>45</v>
+      </c>
+      <c r="L127" s="6">
+        <v>50</v>
       </c>
       <c r="M127" s="4"/>
       <c r="N127" s="4"/>
       <c r="O127" s="4"/>
       <c r="P127" s="4"/>
       <c r="Q127" s="43"/>
-      <c r="R127" s="56" t="s">
-        <v>229</v>
+      <c r="R127" s="63" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="128" spans="2:20">
       <c r="B128" s="105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>271</v>
+        <v>163</v>
       </c>
       <c r="D128" s="22">
+        <v>0.02</v>
+      </c>
+      <c r="E128" s="22">
+        <v>0.03</v>
+      </c>
+      <c r="F128" s="22">
         <v>0.04</v>
       </c>
-      <c r="E128" s="22">
+      <c r="G128" s="22">
+        <v>0.05</v>
+      </c>
+      <c r="H128" s="22">
         <v>0.06</v>
       </c>
-      <c r="F128" s="22">
+      <c r="I128" s="22">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J128" s="22">
         <v>0.08</v>
       </c>
-      <c r="G128" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="H128" s="60"/>
-      <c r="I128" s="61"/>
-      <c r="J128" s="61"/>
-      <c r="K128" s="61"/>
-      <c r="L128" s="61"/>
+      <c r="K128" s="22">
+        <v>0.09</v>
+      </c>
+      <c r="L128" s="22">
+        <v>0.11</v>
+      </c>
       <c r="M128" s="4"/>
       <c r="N128" s="4"/>
       <c r="O128" s="4"/>
       <c r="P128" s="4"/>
       <c r="Q128" s="43"/>
       <c r="R128" s="56" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
     </row>
     <row r="129" spans="2:18">
       <c r="B129" s="105" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="D129" s="22">
         <v>0.04</v>
@@ -8522,36 +8546,26 @@
       <c r="G129" s="22">
         <v>0.1</v>
       </c>
-      <c r="H129" s="22">
-        <v>0.12</v>
-      </c>
-      <c r="I129" s="22">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="J129" s="22">
-        <v>0.16</v>
-      </c>
-      <c r="K129" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="L129" s="22">
-        <v>0.2</v>
-      </c>
+      <c r="H129" s="60"/>
+      <c r="I129" s="61"/>
+      <c r="J129" s="61"/>
+      <c r="K129" s="61"/>
+      <c r="L129" s="61"/>
       <c r="M129" s="4"/>
       <c r="N129" s="4"/>
       <c r="O129" s="4"/>
       <c r="P129" s="4"/>
       <c r="Q129" s="43"/>
       <c r="R129" s="56" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
     </row>
     <row r="130" spans="2:18">
       <c r="B130" s="105" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D130" s="22">
         <v>0.04</v>
@@ -8586,408 +8600,398 @@
       <c r="P130" s="4"/>
       <c r="Q130" s="43"/>
       <c r="R130" s="56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="131" spans="2:18">
       <c r="B131" s="105" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D131" s="6">
-        <v>2</v>
-      </c>
-      <c r="E131" s="6">
-        <v>3</v>
-      </c>
-      <c r="F131" s="6">
-        <v>4</v>
-      </c>
-      <c r="G131" s="6">
-        <v>5</v>
-      </c>
-      <c r="H131" s="6">
-        <v>6</v>
-      </c>
-      <c r="I131" s="6">
-        <v>7</v>
-      </c>
-      <c r="J131" s="6">
-        <v>8</v>
-      </c>
-      <c r="K131" s="6">
-        <v>9</v>
-      </c>
-      <c r="L131" s="6">
-        <v>10</v>
-      </c>
-      <c r="M131" s="6">
-        <v>11</v>
-      </c>
-      <c r="N131" s="6">
-        <v>12</v>
-      </c>
-      <c r="O131" s="6">
-        <v>13</v>
-      </c>
-      <c r="P131" s="6">
-        <v>14</v>
-      </c>
-      <c r="Q131" s="44">
-        <v>15</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="D131" s="22">
+        <v>0.04</v>
+      </c>
+      <c r="E131" s="22">
+        <v>0.06</v>
+      </c>
+      <c r="F131" s="22">
+        <v>0.08</v>
+      </c>
+      <c r="G131" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="H131" s="22">
+        <v>0.12</v>
+      </c>
+      <c r="I131" s="22">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J131" s="22">
+        <v>0.16</v>
+      </c>
+      <c r="K131" s="22">
+        <v>0.18</v>
+      </c>
+      <c r="L131" s="22">
+        <v>0.2</v>
+      </c>
+      <c r="M131" s="4"/>
+      <c r="N131" s="4"/>
+      <c r="O131" s="4"/>
+      <c r="P131" s="4"/>
+      <c r="Q131" s="43"/>
       <c r="R131" s="56" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="132" spans="2:18">
       <c r="B132" s="105" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D132" s="6">
+        <v>2</v>
+      </c>
+      <c r="E132" s="6">
+        <v>3</v>
+      </c>
+      <c r="F132" s="6">
+        <v>4</v>
+      </c>
+      <c r="G132" s="6">
+        <v>5</v>
+      </c>
+      <c r="H132" s="6">
+        <v>6</v>
+      </c>
+      <c r="I132" s="6">
+        <v>7</v>
+      </c>
+      <c r="J132" s="6">
         <v>8</v>
       </c>
-      <c r="C132" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="D132" s="22">
-        <v>0.06</v>
-      </c>
-      <c r="E132" s="22">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F132" s="22">
-        <v>0.08</v>
-      </c>
-      <c r="G132" s="22">
-        <v>0.09</v>
-      </c>
-      <c r="H132" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="I132" s="22">
-        <v>0.11</v>
-      </c>
-      <c r="J132" s="22">
-        <v>0.12</v>
-      </c>
-      <c r="K132" s="22">
-        <v>0.13</v>
-      </c>
-      <c r="L132" s="22">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="M132" s="32">
-        <v>0.15</v>
-      </c>
-      <c r="N132" s="32">
-        <v>0.16</v>
-      </c>
-      <c r="O132" s="32">
-        <v>0.17</v>
-      </c>
-      <c r="P132" s="32">
-        <v>0.18</v>
-      </c>
-      <c r="Q132" s="51">
-        <v>0.2</v>
+      <c r="K132" s="6">
+        <v>9</v>
+      </c>
+      <c r="L132" s="6">
+        <v>10</v>
+      </c>
+      <c r="M132" s="6">
+        <v>11</v>
+      </c>
+      <c r="N132" s="6">
+        <v>12</v>
+      </c>
+      <c r="O132" s="6">
+        <v>13</v>
+      </c>
+      <c r="P132" s="6">
+        <v>14</v>
+      </c>
+      <c r="Q132" s="44">
+        <v>15</v>
       </c>
       <c r="R132" s="56" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
     </row>
     <row r="133" spans="2:18">
       <c r="B133" s="105" t="s">
+        <v>8</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D133" s="22">
+        <v>0.06</v>
+      </c>
+      <c r="E133" s="22">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F133" s="22">
+        <v>0.08</v>
+      </c>
+      <c r="G133" s="22">
+        <v>0.09</v>
+      </c>
+      <c r="H133" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="I133" s="22">
+        <v>0.11</v>
+      </c>
+      <c r="J133" s="22">
+        <v>0.12</v>
+      </c>
+      <c r="K133" s="22">
+        <v>0.13</v>
+      </c>
+      <c r="L133" s="22">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M133" s="32">
+        <v>0.15</v>
+      </c>
+      <c r="N133" s="32">
+        <v>0.16</v>
+      </c>
+      <c r="O133" s="32">
+        <v>0.17</v>
+      </c>
+      <c r="P133" s="32">
+        <v>0.18</v>
+      </c>
+      <c r="Q133" s="51">
+        <v>0.2</v>
+      </c>
+      <c r="R133" s="56" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="134" spans="2:18">
+      <c r="B134" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="C133" s="6" t="s">
+      <c r="C134" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D133" s="22">
+      <c r="D134" s="22">
         <v>0.1</v>
       </c>
-      <c r="E133" s="22">
+      <c r="E134" s="22">
         <v>0.15</v>
       </c>
-      <c r="F133" s="22">
+      <c r="F134" s="22">
         <v>0.2</v>
       </c>
-      <c r="G133" s="22">
+      <c r="G134" s="22">
         <v>0.25</v>
       </c>
-      <c r="H133" s="22">
+      <c r="H134" s="22">
         <v>0.3</v>
       </c>
-      <c r="I133" s="22">
+      <c r="I134" s="22">
         <v>0.35</v>
       </c>
-      <c r="J133" s="22">
+      <c r="J134" s="22">
         <v>0.4</v>
       </c>
-      <c r="K133" s="22">
+      <c r="K134" s="22">
         <v>0.45</v>
       </c>
-      <c r="L133" s="22">
+      <c r="L134" s="22">
         <v>0.5</v>
       </c>
-      <c r="M133" s="32">
+      <c r="M134" s="32">
         <v>0.53</v>
       </c>
-      <c r="N133" s="32">
+      <c r="N134" s="32">
         <v>0.56000000000000005</v>
       </c>
-      <c r="O133" s="32">
+      <c r="O134" s="32">
         <v>0.59</v>
       </c>
-      <c r="P133" s="32">
+      <c r="P134" s="32">
         <v>0.62</v>
       </c>
-      <c r="Q133" s="51">
+      <c r="Q134" s="51">
         <v>0.65</v>
-      </c>
-      <c r="R133" s="56" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="134" spans="2:18">
-      <c r="B134" s="106" t="s">
-        <v>180</v>
-      </c>
-      <c r="C134" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="D134" s="32">
-        <v>0.27</v>
-      </c>
-      <c r="E134" s="32">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="F134" s="32">
-        <v>0.31</v>
-      </c>
-      <c r="G134" s="32">
-        <v>0.33</v>
-      </c>
-      <c r="H134" s="32">
-        <v>0.35</v>
-      </c>
-      <c r="I134" s="32">
-        <v>0.37</v>
-      </c>
-      <c r="J134" s="32">
-        <v>0.39</v>
-      </c>
-      <c r="K134" s="32">
-        <v>0.41</v>
-      </c>
-      <c r="L134" s="32">
-        <v>0.43</v>
-      </c>
-      <c r="M134" s="32">
-        <v>0.45</v>
-      </c>
-      <c r="N134" s="32">
-        <v>0.47</v>
-      </c>
-      <c r="O134" s="32">
-        <v>0.49</v>
-      </c>
-      <c r="P134" s="32">
-        <v>0.51</v>
-      </c>
-      <c r="Q134" s="32">
-        <v>0.55000000000000004</v>
       </c>
       <c r="R134" s="56" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="135" spans="2:18">
-      <c r="B135" s="107" t="s">
+      <c r="B135" s="106" t="s">
+        <v>180</v>
+      </c>
+      <c r="C135" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D135" s="32">
+        <v>0.27</v>
+      </c>
+      <c r="E135" s="32">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F135" s="32">
+        <v>0.31</v>
+      </c>
+      <c r="G135" s="32">
+        <v>0.33</v>
+      </c>
+      <c r="H135" s="32">
+        <v>0.35</v>
+      </c>
+      <c r="I135" s="32">
+        <v>0.37</v>
+      </c>
+      <c r="J135" s="32">
+        <v>0.39</v>
+      </c>
+      <c r="K135" s="32">
+        <v>0.41</v>
+      </c>
+      <c r="L135" s="32">
+        <v>0.43</v>
+      </c>
+      <c r="M135" s="32">
+        <v>0.45</v>
+      </c>
+      <c r="N135" s="32">
+        <v>0.47</v>
+      </c>
+      <c r="O135" s="32">
+        <v>0.49</v>
+      </c>
+      <c r="P135" s="32">
+        <v>0.51</v>
+      </c>
+      <c r="Q135" s="32">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R135" s="56" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="136" spans="2:18">
+      <c r="B136" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="C135" s="7" t="s">
+      <c r="C136" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D135" s="8">
+      <c r="D136" s="8">
         <v>0.1</v>
       </c>
-      <c r="E135" s="8">
+      <c r="E136" s="8">
         <v>0.15</v>
       </c>
-      <c r="F135" s="8">
+      <c r="F136" s="8">
         <v>0.2</v>
       </c>
-      <c r="G135" s="8">
+      <c r="G136" s="8">
         <v>0.25</v>
       </c>
-      <c r="H135" s="8">
+      <c r="H136" s="8">
         <v>0.3</v>
       </c>
-      <c r="I135" s="8">
+      <c r="I136" s="8">
         <v>0.35</v>
       </c>
-      <c r="J135" s="8">
+      <c r="J136" s="8">
         <v>0.4</v>
       </c>
-      <c r="K135" s="8">
+      <c r="K136" s="8">
         <v>0.45</v>
       </c>
-      <c r="L135" s="8">
+      <c r="L136" s="8">
         <v>0.5</v>
       </c>
-      <c r="M135" s="75"/>
-      <c r="N135" s="76"/>
-      <c r="O135" s="76"/>
-      <c r="P135" s="76"/>
-      <c r="Q135" s="77"/>
-      <c r="R135" s="56" t="s">
+      <c r="M136" s="75"/>
+      <c r="N136" s="76"/>
+      <c r="O136" s="76"/>
+      <c r="P136" s="76"/>
+      <c r="Q136" s="77"/>
+      <c r="R136" s="56" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="136" spans="2:18">
-      <c r="B136" s="108" t="s">
+    <row r="137" spans="2:18">
+      <c r="B137" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="C136" s="16" t="s">
+      <c r="C137" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="D136" s="30">
+      <c r="D137" s="30">
         <v>0.06</v>
       </c>
-      <c r="E136" s="30">
+      <c r="E137" s="30">
         <v>0.09</v>
       </c>
-      <c r="F136" s="30">
+      <c r="F137" s="30">
         <v>0.12</v>
       </c>
-      <c r="G136" s="30">
+      <c r="G137" s="30">
         <v>0.15</v>
       </c>
-      <c r="H136" s="30">
+      <c r="H137" s="30">
         <v>0.18</v>
       </c>
-      <c r="I136" s="30">
+      <c r="I137" s="30">
         <v>0.21</v>
       </c>
-      <c r="J136" s="30">
+      <c r="J137" s="30">
         <v>0.24</v>
       </c>
-      <c r="K136" s="30">
+      <c r="K137" s="30">
         <v>0.27</v>
       </c>
-      <c r="L136" s="62">
+      <c r="L137" s="62">
         <v>0.3</v>
       </c>
-      <c r="M136" s="2"/>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
-      <c r="P136" s="2"/>
-      <c r="Q136" s="78"/>
-      <c r="R136" s="56" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="137" spans="2:18">
-      <c r="B137" s="109" t="s">
-        <v>182</v>
-      </c>
-      <c r="C137" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="D137" s="79">
-        <v>0.12</v>
-      </c>
-      <c r="E137" s="79">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="F137" s="79">
-        <v>0.16</v>
-      </c>
-      <c r="G137" s="79">
-        <v>0.18</v>
-      </c>
-      <c r="H137" s="79">
-        <v>0.2</v>
-      </c>
-      <c r="I137" s="79">
-        <v>0.22</v>
-      </c>
-      <c r="J137" s="79">
-        <v>0.24</v>
-      </c>
-      <c r="K137" s="79">
-        <v>0.26</v>
-      </c>
-      <c r="L137" s="32">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="M137" s="32">
-        <v>0.3</v>
-      </c>
-      <c r="N137" s="32">
-        <v>0.32</v>
-      </c>
-      <c r="O137" s="32">
-        <v>0.34</v>
-      </c>
-      <c r="P137" s="32">
-        <v>0.36</v>
-      </c>
-      <c r="Q137" s="32">
-        <v>0.4</v>
-      </c>
+      <c r="M137" s="2"/>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" s="2"/>
+      <c r="Q137" s="78"/>
       <c r="R137" s="56" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="138" spans="2:18">
       <c r="B138" s="109" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C138" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="D138" s="29">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E138" s="29">
-        <v>0.64</v>
+        <v>183</v>
+      </c>
+      <c r="D138" s="79">
+        <v>0.12</v>
+      </c>
+      <c r="E138" s="79">
+        <v>0.14000000000000001</v>
       </c>
       <c r="F138" s="79">
-        <v>0.71</v>
+        <v>0.16</v>
       </c>
       <c r="G138" s="79">
-        <v>0.78</v>
+        <v>0.18</v>
       </c>
       <c r="H138" s="79">
-        <v>0.85</v>
+        <v>0.2</v>
       </c>
       <c r="I138" s="79">
-        <v>0.92</v>
+        <v>0.22</v>
       </c>
       <c r="J138" s="79">
-        <v>0.99</v>
+        <v>0.24</v>
       </c>
       <c r="K138" s="79">
-        <v>1.06</v>
-      </c>
-      <c r="L138" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="M138" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="N138" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="O138" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="P138" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q138" s="32" t="s">
-        <v>234</v>
+        <v>0.26</v>
+      </c>
+      <c r="L138" s="32">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M138" s="32">
+        <v>0.3</v>
+      </c>
+      <c r="N138" s="32">
+        <v>0.32</v>
+      </c>
+      <c r="O138" s="32">
+        <v>0.34</v>
+      </c>
+      <c r="P138" s="32">
+        <v>0.36</v>
+      </c>
+      <c r="Q138" s="32">
+        <v>0.4</v>
       </c>
       <c r="R138" s="56" t="s">
         <v>205</v>
@@ -8995,199 +8999,252 @@
     </row>
     <row r="139" spans="2:18">
       <c r="B139" s="109" t="s">
+        <v>184</v>
+      </c>
+      <c r="C139" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="D139" s="29">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E139" s="29">
+        <v>0.64</v>
+      </c>
+      <c r="F139" s="79">
+        <v>0.71</v>
+      </c>
+      <c r="G139" s="79">
+        <v>0.78</v>
+      </c>
+      <c r="H139" s="79">
+        <v>0.85</v>
+      </c>
+      <c r="I139" s="79">
+        <v>0.92</v>
+      </c>
+      <c r="J139" s="79">
+        <v>0.99</v>
+      </c>
+      <c r="K139" s="79">
+        <v>1.06</v>
+      </c>
+      <c r="L139" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="M139" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="N139" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="O139" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="P139" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q139" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="R139" s="56" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="140" spans="2:18">
+      <c r="B140" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="C139" s="14" t="s">
+      <c r="C140" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D139" s="30">
+      <c r="D140" s="30">
         <v>0.06</v>
       </c>
-      <c r="E139" s="30">
+      <c r="E140" s="30">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F139" s="30">
+      <c r="F140" s="30">
         <v>0.08</v>
       </c>
-      <c r="G139" s="30">
+      <c r="G140" s="30">
         <v>0.09</v>
       </c>
-      <c r="H139" s="31"/>
-      <c r="I139" s="28"/>
-      <c r="J139" s="28"/>
-      <c r="K139" s="28"/>
-      <c r="L139" s="28"/>
-      <c r="M139" s="2"/>
-      <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
-      <c r="P139" s="2"/>
-      <c r="Q139" s="78"/>
-      <c r="R139" s="56" t="s">
+      <c r="H140" s="31"/>
+      <c r="I140" s="28"/>
+      <c r="J140" s="28"/>
+      <c r="K140" s="28"/>
+      <c r="L140" s="28"/>
+      <c r="M140" s="2"/>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
+      <c r="P140" s="2"/>
+      <c r="Q140" s="78"/>
+      <c r="R140" s="56" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="140" spans="2:18">
-      <c r="B140" s="110" t="s">
+    <row r="141" spans="2:18">
+      <c r="B141" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="C140" s="14" t="s">
+      <c r="C141" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="D140" s="30">
+      <c r="D141" s="30">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E140" s="30">
+      <c r="E141" s="30">
         <v>0.09</v>
       </c>
-      <c r="F140" s="30">
+      <c r="F141" s="30">
         <v>0.11</v>
       </c>
-      <c r="G140" s="30">
+      <c r="G141" s="30">
         <v>0.13</v>
       </c>
-      <c r="H140" s="30">
+      <c r="H141" s="30">
         <v>0.15</v>
       </c>
-      <c r="I140" s="30">
+      <c r="I141" s="30">
         <v>0.17</v>
       </c>
-      <c r="J140" s="30">
+      <c r="J141" s="30">
         <v>0.19</v>
       </c>
-      <c r="K140" s="30">
+      <c r="K141" s="30">
         <v>0.21</v>
       </c>
-      <c r="L140" s="30">
+      <c r="L141" s="30">
         <v>0.23</v>
       </c>
-      <c r="M140" s="30">
+      <c r="M141" s="30">
         <v>0.25</v>
       </c>
-      <c r="N140" s="30">
+      <c r="N141" s="30">
         <v>0.27</v>
       </c>
-      <c r="O140" s="30">
+      <c r="O141" s="30">
         <v>0.28999999999999998</v>
       </c>
-      <c r="P140" s="30">
+      <c r="P141" s="30">
         <v>0.31</v>
       </c>
-      <c r="Q140" s="80">
+      <c r="Q141" s="80">
         <v>0.33</v>
       </c>
-      <c r="R140" s="56" t="s">
+      <c r="R141" s="56" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="141" spans="2:18">
-      <c r="B141" s="108" t="s">
+    <row r="142" spans="2:18">
+      <c r="B142" s="108" t="s">
         <v>187</v>
       </c>
-      <c r="C141" s="14" t="s">
+      <c r="C142" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="D141" s="30">
+      <c r="D142" s="30">
         <v>0.02</v>
       </c>
-      <c r="E141" s="30">
+      <c r="E142" s="30">
         <v>0.03</v>
       </c>
-      <c r="F141" s="62">
+      <c r="F142" s="62">
         <v>0.04</v>
       </c>
-      <c r="G141" s="30">
+      <c r="G142" s="30">
         <v>0.05</v>
       </c>
-      <c r="H141" s="30">
+      <c r="H142" s="30">
         <v>0.06</v>
       </c>
-      <c r="I141" s="30">
+      <c r="I142" s="30">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J141" s="30">
+      <c r="J142" s="30">
         <v>0.08</v>
       </c>
-      <c r="K141" s="30">
+      <c r="K142" s="30">
         <v>0.09</v>
       </c>
-      <c r="L141" s="30">
+      <c r="L142" s="30">
         <v>0.1</v>
       </c>
-      <c r="M141" s="32" t="s">
+      <c r="M142" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="N141" s="32" t="s">
+      <c r="N142" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="O141" s="32" t="s">
+      <c r="O142" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="P141" s="32" t="s">
+      <c r="P142" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="Q141" s="32" t="s">
+      <c r="Q142" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="R141" s="56" t="s">
+      <c r="R142" s="56" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="142" spans="2:18" ht="14.65" thickBot="1">
-      <c r="B142" s="111" t="s">
+    <row r="143" spans="2:18" ht="14.65" thickBot="1">
+      <c r="B143" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="C142" s="9" t="s">
+      <c r="C143" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="D142" s="10">
+      <c r="D143" s="10">
         <v>0.02</v>
       </c>
-      <c r="E142" s="10">
+      <c r="E143" s="10">
         <v>0.03</v>
       </c>
-      <c r="F142" s="11">
+      <c r="F143" s="11">
         <v>0.04</v>
       </c>
-      <c r="G142" s="10">
+      <c r="G143" s="10">
         <v>0.05</v>
       </c>
-      <c r="H142" s="10">
+      <c r="H143" s="10">
         <v>0.06</v>
       </c>
-      <c r="I142" s="10">
+      <c r="I143" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J142" s="10">
+      <c r="J143" s="10">
         <v>0.08</v>
       </c>
-      <c r="K142" s="10">
+      <c r="K143" s="10">
         <v>0.09</v>
       </c>
-      <c r="L142" s="10">
+      <c r="L143" s="10">
         <v>0.1</v>
       </c>
-      <c r="M142" s="50">
+      <c r="M143" s="50">
         <v>0.11</v>
       </c>
-      <c r="N142" s="33">
+      <c r="N143" s="33">
         <v>0.12</v>
       </c>
-      <c r="O142" s="33">
+      <c r="O143" s="33">
         <v>0.13</v>
       </c>
-      <c r="P142" s="33">
+      <c r="P143" s="33">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Q142" s="34">
+      <c r="Q143" s="34">
         <v>0.15</v>
       </c>
-      <c r="R142" s="58" t="s">
+      <c r="R143" s="58" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="143" spans="2:18" ht="14.65" thickTop="1"/>
-    <row r="150" spans="3:3">
-      <c r="C150" s="104"/>
+    <row r="144" spans="2:18" ht="14.65" thickTop="1"/>
+    <row r="151" spans="3:3">
+      <c r="C151" s="104"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9195,20 +9252,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9431,14 +9488,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53964A40-A6D0-45D9-B1D4-1342A31D1BCB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -9451,6 +9500,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data-source/技能数据.xlsx
+++ b/data-source/技能数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D22D29C-7558-4338-8E42-5FA0E310BBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A506305-9A9A-41AA-A190-A20D815916E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F03E0F5E-A49D-457A-ADAE-8FAE4055FE2C}"/>
   </bookViews>
@@ -1333,9 +1333,6 @@
     <t>Lv1-Lv4：4级图；Lv1-Lv8：5级图/城堡；Lv5-Lv10：大车炮台；Lv6-Lv10：酷吏地下城</t>
   </si>
   <si>
-    <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士</t>
-  </si>
-  <si>
     <t>Lv1-Lv6：叛徒地下墓穴；Lv7-Lv8：商人护送；Lv1-Lv8：酷吏地下城</t>
   </si>
   <si>
@@ -1608,6 +1605,9 @@
   </si>
   <si>
     <t>下一次攻击会造成伤口，使目标受到的治疗效果降低35%，持续10秒</t>
+  </si>
+  <si>
+    <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士；Lv1-Lv10：大车炮台</t>
   </si>
 </sst>
 </file>
@@ -3225,7 +3225,7 @@
       <c r="P3" s="35"/>
       <c r="Q3" s="35"/>
       <c r="R3" s="68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="2:21" ht="41.65">
@@ -3268,7 +3268,7 @@
       <c r="P4" s="35"/>
       <c r="Q4" s="35"/>
       <c r="R4" s="68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="2:21" ht="41.65">
@@ -3293,7 +3293,7 @@
       <c r="P5" s="53"/>
       <c r="Q5" s="65"/>
       <c r="R5" s="68" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="2:21" ht="41.65">
@@ -3346,7 +3346,7 @@
         <v>90</v>
       </c>
       <c r="R6" s="68" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="2:21">
@@ -3452,7 +3452,7 @@
         <v>36</v>
       </c>
       <c r="R8" s="68" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="2:21" ht="41.65">
@@ -3505,7 +3505,7 @@
         <v>1.2</v>
       </c>
       <c r="R9" s="68" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="2:21" ht="41.65">
@@ -3558,7 +3558,7 @@
         <v>1.2</v>
       </c>
       <c r="R10" s="68" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="2:21">
@@ -3611,7 +3611,7 @@
         <v>15</v>
       </c>
       <c r="R11" s="68" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="2:21">
@@ -3775,10 +3775,10 @@
     </row>
     <row r="15" spans="2:21">
       <c r="B15" s="83" t="s">
+        <v>281</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>282</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>283</v>
       </c>
       <c r="D15" s="8">
         <v>0.38</v>
@@ -3973,7 +3973,7 @@
       <c r="P19" s="35"/>
       <c r="Q19" s="35"/>
       <c r="R19" s="68" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="2:20">
@@ -4002,7 +4002,7 @@
       <c r="P20" s="35"/>
       <c r="Q20" s="35"/>
       <c r="R20" s="68" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" spans="2:20">
@@ -4031,7 +4031,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
       <c r="R21" s="68" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="2:20">
@@ -4060,7 +4060,7 @@
       <c r="P22" s="35"/>
       <c r="Q22" s="35"/>
       <c r="R22" s="68" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" spans="2:20" ht="27.75">
@@ -4091,7 +4091,7 @@
       <c r="P23" s="35"/>
       <c r="Q23" s="35"/>
       <c r="R23" s="68" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="2:20" ht="27.75">
@@ -4122,7 +4122,7 @@
       <c r="P24" s="35"/>
       <c r="Q24" s="35"/>
       <c r="R24" s="68" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="2:20" ht="27.75">
@@ -4155,7 +4155,7 @@
       <c r="P25" s="35"/>
       <c r="Q25" s="35"/>
       <c r="R25" s="68" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="2:20" ht="27.75">
@@ -4188,7 +4188,7 @@
       <c r="P26" s="35"/>
       <c r="Q26" s="35"/>
       <c r="R26" s="68" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" spans="2:20" ht="27.75">
@@ -4221,7 +4221,7 @@
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
       <c r="R27" s="68" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="2:20" ht="27.75">
@@ -4256,7 +4256,7 @@
       <c r="P28" s="35"/>
       <c r="Q28" s="35"/>
       <c r="R28" s="68" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29" spans="2:20" ht="27.75">
@@ -4291,7 +4291,7 @@
       <c r="P29" s="35"/>
       <c r="Q29" s="35"/>
       <c r="R29" s="68" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" spans="2:20" ht="28.15" thickBot="1">
@@ -4326,7 +4326,7 @@
       <c r="P30" s="35"/>
       <c r="Q30" s="35"/>
       <c r="R30" s="68" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="31" spans="2:20" ht="42" thickBot="1">
@@ -4363,7 +4363,7 @@
       <c r="P31" s="35"/>
       <c r="Q31" s="35"/>
       <c r="R31" s="68" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="T31" s="52"/>
     </row>
@@ -4403,7 +4403,7 @@
       <c r="P32" s="35"/>
       <c r="Q32" s="35"/>
       <c r="R32" s="68" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" spans="2:18">
@@ -4442,7 +4442,7 @@
       <c r="P33" s="35"/>
       <c r="Q33" s="35"/>
       <c r="R33" s="68" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="2:18" ht="41.65">
@@ -4481,7 +4481,7 @@
       <c r="P34" s="35"/>
       <c r="Q34" s="35"/>
       <c r="R34" s="68" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="2:18" ht="27.75">
@@ -4522,7 +4522,7 @@
       <c r="P35" s="35"/>
       <c r="Q35" s="35"/>
       <c r="R35" s="68" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36" spans="2:18">
@@ -4628,7 +4628,7 @@
         <v>15</v>
       </c>
       <c r="R37" s="68" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38" spans="2:18">
@@ -4734,7 +4734,7 @@
         <v>15</v>
       </c>
       <c r="R39" s="68" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40" spans="2:18">
@@ -4787,7 +4787,7 @@
         <v>15</v>
       </c>
       <c r="R40" s="71" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="2:18">
@@ -4946,7 +4946,7 @@
         <v>0.3</v>
       </c>
       <c r="R43" s="71" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="2:18">
@@ -4999,7 +4999,7 @@
         <v>0.4</v>
       </c>
       <c r="R44" s="71" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="45" spans="2:18" ht="14.65" thickBot="1">
@@ -5166,7 +5166,7 @@
       <c r="P48" s="35"/>
       <c r="Q48" s="35"/>
       <c r="R48" s="73" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" spans="2:18" ht="42.75">
@@ -5209,7 +5209,7 @@
       <c r="P49" s="35"/>
       <c r="Q49" s="35"/>
       <c r="R49" s="73" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" spans="2:18" ht="42.75">
@@ -5252,7 +5252,7 @@
       <c r="P50" s="35"/>
       <c r="Q50" s="35"/>
       <c r="R50" s="73" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="51" spans="2:18" ht="42.75">
@@ -5295,7 +5295,7 @@
       <c r="P51" s="35"/>
       <c r="Q51" s="35"/>
       <c r="R51" s="73" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="52" spans="2:18" ht="42.75">
@@ -5338,7 +5338,7 @@
       <c r="P52" s="35"/>
       <c r="Q52" s="35"/>
       <c r="R52" s="73" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="53" spans="2:18" ht="42.75">
@@ -5381,7 +5381,7 @@
       <c r="P53" s="35"/>
       <c r="Q53" s="35"/>
       <c r="R53" s="73" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="54" spans="2:18" ht="42.75">
@@ -5424,7 +5424,7 @@
       <c r="P54" s="35"/>
       <c r="Q54" s="35"/>
       <c r="R54" s="73" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="55" spans="2:18" ht="42.75">
@@ -5467,7 +5467,7 @@
       <c r="P55" s="35"/>
       <c r="Q55" s="35"/>
       <c r="R55" s="73" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="56" spans="2:18">
@@ -5502,7 +5502,7 @@
       <c r="P56" s="35"/>
       <c r="Q56" s="35"/>
       <c r="R56" s="71" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="57" spans="2:18">
@@ -5537,7 +5537,7 @@
       <c r="P57" s="35"/>
       <c r="Q57" s="35"/>
       <c r="R57" s="71" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="58" spans="2:18">
@@ -5572,7 +5572,7 @@
       <c r="P58" s="35"/>
       <c r="Q58" s="35"/>
       <c r="R58" s="71" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="59" spans="2:18" ht="14.65" thickBot="1">
@@ -5607,7 +5607,7 @@
       <c r="P59" s="48"/>
       <c r="Q59" s="48"/>
       <c r="R59" s="72" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="60" spans="2:18" ht="15" thickTop="1" thickBot="1">
@@ -5721,7 +5721,7 @@
       <c r="P62" s="35"/>
       <c r="Q62" s="35"/>
       <c r="R62" s="73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="63" spans="2:18" ht="28.5">
@@ -5764,7 +5764,7 @@
       <c r="P63" s="35"/>
       <c r="Q63" s="35"/>
       <c r="R63" s="73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="64" spans="2:18" ht="28.5">
@@ -5807,7 +5807,7 @@
       <c r="P64" s="35"/>
       <c r="Q64" s="35"/>
       <c r="R64" s="73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="65" spans="2:18" ht="28.5">
@@ -5850,7 +5850,7 @@
       <c r="P65" s="35"/>
       <c r="Q65" s="35"/>
       <c r="R65" s="73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="2:18" ht="28.5">
@@ -5893,7 +5893,7 @@
       <c r="P66" s="35"/>
       <c r="Q66" s="35"/>
       <c r="R66" s="73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="67" spans="2:18" ht="28.5">
@@ -5936,7 +5936,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="35"/>
       <c r="R67" s="73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="68" spans="2:18" ht="28.5">
@@ -5979,7 +5979,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="35"/>
       <c r="R68" s="73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="69" spans="2:18">
@@ -6151,7 +6151,7 @@
       <c r="P72" s="35"/>
       <c r="Q72" s="35"/>
       <c r="R72" s="71" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="73" spans="2:18">
@@ -6194,7 +6194,7 @@
       <c r="P73" s="35"/>
       <c r="Q73" s="35"/>
       <c r="R73" s="71" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="74" spans="2:18">
@@ -6237,7 +6237,7 @@
       <c r="P74" s="35"/>
       <c r="Q74" s="35"/>
       <c r="R74" s="71" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="75" spans="2:18">
@@ -6280,7 +6280,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="35"/>
       <c r="R75" s="71" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76" spans="2:18">
@@ -6323,7 +6323,7 @@
       <c r="P76" s="35"/>
       <c r="Q76" s="35"/>
       <c r="R76" s="71" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="77" spans="2:18">
@@ -6460,7 +6460,7 @@
         <v>72</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D80" s="6">
         <v>2</v>
@@ -6753,7 +6753,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
       <c r="R86" s="73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="87" spans="2:18" ht="28.5">
@@ -6796,7 +6796,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
       <c r="R87" s="73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="88" spans="2:18" ht="28.5">
@@ -6839,7 +6839,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
       <c r="R88" s="73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="89" spans="2:18">
@@ -7097,7 +7097,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
       <c r="R94" s="71" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="95" spans="2:18">
@@ -7140,7 +7140,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
       <c r="R95" s="71" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="96" spans="2:18">
@@ -7366,7 +7366,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
       <c r="R101" s="73" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="102" spans="2:18">
@@ -7452,7 +7452,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
       <c r="R103" s="73" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="104" spans="2:18" ht="42.75">
@@ -7495,7 +7495,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
       <c r="R104" s="73" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="105" spans="2:18">
@@ -7581,7 +7581,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
       <c r="R106" s="73" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="107" spans="2:18" ht="43.15" thickBot="1">
@@ -7624,7 +7624,7 @@
       <c r="P107" s="48"/>
       <c r="Q107" s="48"/>
       <c r="R107" s="74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="108" spans="2:18" ht="15" thickTop="1" thickBot="1"/>
@@ -7721,7 +7721,7 @@
       <c r="P110" s="4"/>
       <c r="Q110" s="43"/>
       <c r="R110" s="73" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="111" spans="2:18" ht="42.75">
@@ -7774,7 +7774,7 @@
         <v>30</v>
       </c>
       <c r="R111" s="73" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="112" spans="2:18" ht="42.75">
@@ -7817,7 +7817,7 @@
       <c r="P112" s="4"/>
       <c r="Q112" s="43"/>
       <c r="R112" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="113" spans="2:20" ht="28.5">
@@ -7860,7 +7860,7 @@
       <c r="P113" s="4"/>
       <c r="Q113" s="43"/>
       <c r="R113" s="73" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="114" spans="2:20" ht="42.75">
@@ -7903,7 +7903,7 @@
       <c r="P114" s="5"/>
       <c r="Q114" s="45"/>
       <c r="R114" s="73" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="115" spans="2:20" ht="42.75">
@@ -7946,7 +7946,7 @@
       <c r="P115" s="4"/>
       <c r="Q115" s="43"/>
       <c r="R115" s="73" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="116" spans="2:20">
@@ -8220,7 +8220,7 @@
         <v>19</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D121" s="22">
         <v>0.08</v>
@@ -8255,7 +8255,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="47"/>
       <c r="R121" s="71" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="122" spans="2:20" ht="14.65" thickBot="1">
@@ -8263,7 +8263,7 @@
         <v>18</v>
       </c>
       <c r="C122" s="18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D122" s="26">
         <v>0.08</v>
@@ -8298,7 +8298,7 @@
       <c r="P122" s="48"/>
       <c r="Q122" s="49"/>
       <c r="R122" s="72" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="123" spans="2:20" ht="15" thickTop="1" thickBot="1"/>
@@ -8395,7 +8395,7 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="43"/>
       <c r="R125" s="63" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="126" spans="2:20" ht="28.5">
@@ -8438,7 +8438,7 @@
       <c r="P126" s="4"/>
       <c r="Q126" s="43"/>
       <c r="R126" s="63" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="127" spans="2:20" ht="28.5">
@@ -8481,7 +8481,7 @@
       <c r="P127" s="4"/>
       <c r="Q127" s="43"/>
       <c r="R127" s="63" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="128" spans="2:20">
@@ -8524,7 +8524,7 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="43"/>
       <c r="R128" s="56" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="129" spans="2:18">
@@ -8532,7 +8532,7 @@
         <v>15</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D129" s="22">
         <v>0.04</v>
@@ -8557,7 +8557,7 @@
       <c r="P129" s="4"/>
       <c r="Q129" s="43"/>
       <c r="R129" s="56" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="130" spans="2:18">
@@ -8704,7 +8704,7 @@
         <v>8</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D133" s="22">
         <v>0.06</v>
@@ -8749,7 +8749,7 @@
         <v>0.2</v>
       </c>
       <c r="R133" s="56" t="s">
-        <v>226</v>
+        <v>283</v>
       </c>
     </row>
     <row r="134" spans="2:18">
@@ -8898,7 +8898,7 @@
       <c r="P136" s="76"/>
       <c r="Q136" s="77"/>
       <c r="R136" s="56" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="137" spans="2:18">
@@ -9029,22 +9029,22 @@
         <v>1.06</v>
       </c>
       <c r="L139" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M139" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N139" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O139" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P139" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q139" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R139" s="56" t="s">
         <v>205</v>
@@ -9080,7 +9080,7 @@
       <c r="P140" s="2"/>
       <c r="Q140" s="78"/>
       <c r="R140" s="56" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="141" spans="2:18">
@@ -9141,7 +9141,7 @@
         <v>187</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D142" s="30">
         <v>0.02</v>
@@ -9171,19 +9171,19 @@
         <v>0.1</v>
       </c>
       <c r="M142" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N142" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O142" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P142" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q142" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R142" s="56" t="s">
         <v>209</v>
@@ -9194,7 +9194,7 @@
         <v>0</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D143" s="10">
         <v>0.02</v>
@@ -9239,7 +9239,7 @@
         <v>0.15</v>
       </c>
       <c r="R143" s="58" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="144" spans="2:18" ht="14.65" thickTop="1"/>
@@ -9252,20 +9252,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9488,6 +9488,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53964A40-A6D0-45D9-B1D4-1342A31D1BCB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -9500,14 +9508,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data-source/技能数据.xlsx
+++ b/data-source/技能数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A506305-9A9A-41AA-A190-A20D815916E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B96ECC-7E96-4EEB-94D0-9FD8BE3ACC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F03E0F5E-A49D-457A-ADAE-8FAE4055FE2C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="285">
   <si>
     <t>格挡大师</t>
   </si>
@@ -1608,6 +1608,9 @@
   </si>
   <si>
     <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士；Lv1-Lv10：大车炮台</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：银矿</t>
   </si>
 </sst>
 </file>
@@ -3822,7 +3825,9 @@
       <c r="Q15" s="70">
         <v>0.8</v>
       </c>
-      <c r="R15" s="68"/>
+      <c r="R15" s="68" t="s">
+        <v>284</v>
+      </c>
       <c r="U15" s="55"/>
     </row>
     <row r="16" spans="2:21" ht="14.65" thickBot="1">
@@ -9252,20 +9257,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9488,14 +9493,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53964A40-A6D0-45D9-B1D4-1342A31D1BCB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -9508,6 +9505,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
